--- a/docs/Fundamentals/2025百大牛股/2025年百大牛股.xlsx
+++ b/docs/Fundamentals/2025百大牛股/2025年百大牛股.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\warrenpyquant\examples\warrenluccie.github.io\docs\Fundamentals\2025百大牛股\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\【0#】DeepReview深度复盘\warrenluccie.github.io\docs\Fundamentals\2025百大牛股\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8FAFE7-513A-4000-8F69-D6C32FE2C94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024B06B7-5983-4642-8AE7-861881F4C31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="328" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="328" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="上纬新材 688585" sheetId="1" r:id="rId1"/>
     <sheet name="天普股份 605255" sheetId="2" r:id="rId2"/>
+    <sheet name="飞沃科技 301232" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="243">
   <si>
     <t>发生日期</t>
   </si>
@@ -667,12 +668,157 @@
     <t>中昊芯英实控人杨龚轶凡成为公司控股股东</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>汽车零部件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>子公司罗博普仑主要开展研发、制造及销售风电叶片专用打磨智能机器人设备业务。</t>
+  </si>
+  <si>
+    <t>商业航天</t>
+  </si>
+  <si>
+    <t>马斯克设想从月球电磁弹射AI卫星 电磁发射有望成商业航天重要方向</t>
+  </si>
+  <si>
+    <t>8058.68万</t>
+  </si>
+  <si>
+    <t>4.24亿</t>
+  </si>
+  <si>
+    <t>商业航天+风电紧固件+扭亏为盈</t>
+  </si>
+  <si>
+    <t>SpaceX收购xAI，总估值达1.25万亿美元|1、据2026年1月5日异动公告，公司在商业航天领域的业务目前处于初始阶段，2025年该业务板块营业收入约123万元，占总营业收入比例为0.05%(未经审计)。公司于2025年12月30日完成了成都新杉宇航科技有限公司60%的股权收购。主营业务为金属3D打印服务，其产品主要包括液体火箭发动机零部件。主要客户为北京天兵科技有限公司，中科宇航技术股份有限公司、星际荣耀航天科技集团股份有限公司、合肥星火空间科技有限公司、西安巨擎科技有限公司、青岛星辰航线科技有限公司、上海大航跃迁航天科技有限公司等。 2、据2025年半年度报告，公司主营风电高强度紧固件，产品覆盖国内外知名风机制造商，市场占有率连续多年稳居行业前列。 3、据2026年1月19日业绩预告，公司预计2025年营收25亿元，归母净利润3200–4500万元，实现扭亏为盈，主要因风电需求旺盛、价格回升及成本下降。</t>
+  </si>
+  <si>
+    <t>银河航天创始人发表演讲 太空新基建将带来万亿级市场爆发期</t>
+  </si>
+  <si>
+    <t>2.16亿</t>
+  </si>
+  <si>
+    <t>6.84亿</t>
+  </si>
+  <si>
+    <t>商业航天+风电紧固件+扭亏</t>
+  </si>
+  <si>
+    <t>马斯克希望7月前让SpaceX上市|公司已用于商业航天项目的产品主要包括商业火箭及火箭发动机所用的紧固件</t>
+  </si>
+  <si>
+    <t>我国新增20万颗卫星申请 专家：卫星频轨资源申请已上升至国家战略层面</t>
+  </si>
+  <si>
+    <t>公司的全资、 控股子公司主要从事风电零部件、 航天紧固件的生产和销售业务</t>
+  </si>
+  <si>
+    <t>2.22亿</t>
+  </si>
+  <si>
+    <t>商业火箭企业适用科创板第五套上市标准细化规则发布|公司已用于商业航天项目的产品主要包括商业火箭及火箭发动机所用的紧固件</t>
+  </si>
+  <si>
+    <t>上交所明确商业火箭科创板上市新规 商业航天产业进入壮大期</t>
+  </si>
+  <si>
+    <t>2025第三届商业航天发展大会即将召开，商业航天进入密集催化期</t>
+  </si>
+  <si>
+    <t>民营太空飞船成功升空 我国商业航天发展迈入新阶段</t>
+  </si>
+  <si>
+    <t>盘中猛拉！A股这一概念，突然大爆发！</t>
+  </si>
+  <si>
+    <t>4.84亿</t>
+  </si>
+  <si>
+    <t>商业航天+实控人增持+风电紧固件</t>
+  </si>
+  <si>
+    <t>OpenAI创始人表示有意在太空建设数据中心；消息称Spacex估值推高到8000亿美元|1、据2025年11月20日公告，公司实际控制人控制的上海弗沃投资管理有限公司计划6个月内增持公司股份，金额不低于4000万元、不超过7000万元，并已取得兴业银行不超过5000万元增持专项贷款承诺函。 2、据公司披露，公司紧固件已用于商业航天项目，主要包括商业火箭及火箭发动机所用紧固件。 3、据公司亮点，公司主营风电高强度紧固件，风电叶片预埋螺套全球市占率约七成，产品覆盖国内外知名风机制造商，市场占有率连续多年稳居行业前列。 4、据2025年12月2日公告，截至11月30日公司已累计回购股份24.24万股，回购金额约1053万元，回购计划仍在推进中。</t>
+  </si>
+  <si>
+    <t>核电核能</t>
+  </si>
+  <si>
+    <t>航空航天+燃气轮机+机器人+风电。1、公司已用于商业航天项目的产品主要包括商业火箭及火箭发动机所用的紧固件。已进入国内多家知名企业的供应商名录，并已开始小批量或批量供货。2、2025年5月6日据官微，公司与全球能源企业GE Vernova签署为期4年的长期合作协议将为对方提供燃气轮机燃烧室钣金件及精密机加件此次合作涉及50余个中标项目。GE Vernova是全球在建燃气电厂燃气轮机市场的领军企业，占据约三分之二的市场份额。3、公司参与C919项目中紧固件、起落架的研发。4、公司风电类高强度紧固件的主要客户群体涵盖国内外风电行业中的知名叶片制造商、整机制造商以及风电场建设和运营商等。5、子公司罗博普仑,专业从事研发、制造及销售风电叶片专用打磨机器人设备业务。</t>
+  </si>
+  <si>
+    <t>四中全会公报新增“航天强国”，相关产业有望迎来重大发展机遇</t>
+  </si>
+  <si>
+    <t>2997.22万</t>
+  </si>
+  <si>
+    <t>5.25亿</t>
+  </si>
+  <si>
+    <t>商业航天+风电紧固件</t>
+  </si>
+  <si>
+    <t>国内海风市场9月迎来招中标高峰期|公司风电类高强度紧固件主要包括风电叶片预埋螺套、整机螺栓（叶片双头螺栓、主机螺栓、塔筒螺栓）和风电锚栓组件等</t>
+  </si>
+  <si>
+    <t>4788.87万</t>
+  </si>
+  <si>
+    <t>4.99亿</t>
+  </si>
+  <si>
+    <t>机器人概念+商业航天+风电</t>
+  </si>
+  <si>
+    <t>陆军首次披露无人化作战模式；9月3日将举行阅兵仪式|公司主要参与了C919起落架、发动机中的紧固件、零部件制造</t>
+  </si>
+  <si>
+    <t>1845.48万</t>
+  </si>
+  <si>
+    <t>7.89亿</t>
+  </si>
+  <si>
+    <t>大飞机+商业航天+风电</t>
+  </si>
+  <si>
+    <t>我国交付老挝航空的首架C909飞机实现商业首航|1、公司主营高强度紧固件，主要应用于风电领域； 2、公司已用于商业航天项目的产品主要包括商业火箭及火箭发动机所用的紧固件</t>
+  </si>
+  <si>
+    <t>行业应用再迎新进展，四足机器人未来市场空间广阔</t>
+  </si>
+  <si>
+    <t>6563.51万</t>
+  </si>
+  <si>
+    <t>8.00亿</t>
+  </si>
+  <si>
+    <t>风电设备</t>
+  </si>
+  <si>
+    <t>风电+航空航天+大飞机+机器人 。1、公司风电类高强度紧固件的主要客户群体涵盖国内外风电行业中的知名叶片制造商、整机制造商以及风电场建设和运营商等。 2、公司航空航天领域的产品已经进入国内多家知名企业的供应商名录，并已开始小批量或批量供货。 3、公司参与C919项目中紧固件、起落架的研发。 4、子公司罗博普仑,专业从事研发、制造及销售风电叶片专用打磨机器人设备业务。</t>
+  </si>
+  <si>
+    <t>公司所属行业为：风电设备</t>
+  </si>
+  <si>
+    <t>2301.90万</t>
+  </si>
+  <si>
+    <t>5.78亿</t>
+  </si>
+  <si>
+    <t>公司已用于商业航天项目的产品主要包括商业火箭及火箭发动机所用的紧固件。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -728,6 +874,12 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -801,7 +953,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -849,6 +1001,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2279,7 +2434,7 @@
     <col min="7" max="7" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>5</v>
       </c>
@@ -2331,7 +2486,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>46066</v>
       </c>
@@ -2347,8 +2502,8 @@
       <c r="E5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>76</v>
+      <c r="F5" s="17" t="s">
+        <v>195</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>77</v>
@@ -3021,7 +3176,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>62</v>
       </c>
@@ -3491,4 +3646,1162 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8305E4-F6FC-4381-8E2B-48ABCD4A0A3E}">
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="255.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>46079</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>46062</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0.56777777777777783</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>46048</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>46045</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.419375</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>46034</v>
+      </c>
+      <c r="B10" s="8">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>46027</v>
+      </c>
+      <c r="B11" s="8">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>46022</v>
+      </c>
+      <c r="B12" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>46021</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>46017</v>
+      </c>
+      <c r="B14" s="8">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>46015</v>
+      </c>
+      <c r="B15" s="8">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>46006</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>46003</v>
+      </c>
+      <c r="B17" s="8">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>46000</v>
+      </c>
+      <c r="B18" s="8">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>45999</v>
+      </c>
+      <c r="B19" s="8">
+        <v>0.47208333333333335</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>45995</v>
+      </c>
+      <c r="B20" s="8">
+        <v>0</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>45985</v>
+      </c>
+      <c r="B21" s="8">
+        <v>0</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>45967</v>
+      </c>
+      <c r="B22" s="8">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>45954</v>
+      </c>
+      <c r="B23" s="8">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>45950</v>
+      </c>
+      <c r="B24" s="8">
+        <v>0.41493055555555558</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>45877</v>
+      </c>
+      <c r="B25" s="8">
+        <v>0.3976736111111111</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>45768</v>
+      </c>
+      <c r="B26" s="8">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>45763</v>
+      </c>
+      <c r="B27" s="8">
+        <v>0.39805555555555555</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>45721</v>
+      </c>
+      <c r="B28" s="8">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="10">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>45714</v>
+      </c>
+      <c r="B29" s="8">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="10">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>45588</v>
+      </c>
+      <c r="B30" s="8">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="10">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>45575</v>
+      </c>
+      <c r="B31" s="8">
+        <v>0.40819444444444447</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>45573</v>
+      </c>
+      <c r="B32" s="8">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="10">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>45565</v>
+      </c>
+      <c r="B33" s="8">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="10">
+        <v>0</v>
+      </c>
+      <c r="E33" s="10">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>45510</v>
+      </c>
+      <c r="B34" s="8">
+        <v>0.39822916666666669</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A35" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B39" s="4">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>46063</v>
+      </c>
+      <c r="B40" s="8">
+        <v>0</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="10">
+        <v>0</v>
+      </c>
+      <c r="E40" s="10">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>46057</v>
+      </c>
+      <c r="B41" s="8">
+        <v>0</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" s="10">
+        <v>0</v>
+      </c>
+      <c r="E41" s="10">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>46037</v>
+      </c>
+      <c r="B42" s="8">
+        <v>0</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="10">
+        <v>0</v>
+      </c>
+      <c r="E42" s="10">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>46035</v>
+      </c>
+      <c r="B43" s="8">
+        <v>0</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" s="10">
+        <v>0</v>
+      </c>
+      <c r="E43" s="10">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>46028</v>
+      </c>
+      <c r="B44" s="8">
+        <v>0</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="10">
+        <v>0</v>
+      </c>
+      <c r="E44" s="10">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>46007</v>
+      </c>
+      <c r="B45" s="8">
+        <v>0</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" s="10">
+        <v>0</v>
+      </c>
+      <c r="E45" s="10">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>45765</v>
+      </c>
+      <c r="B46" s="8">
+        <v>0</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" s="10">
+        <v>0</v>
+      </c>
+      <c r="E46" s="10">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>45754</v>
+      </c>
+      <c r="B47" s="8">
+        <v>0</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D47" s="10">
+        <v>0</v>
+      </c>
+      <c r="E47" s="10">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>45576</v>
+      </c>
+      <c r="B48" s="8">
+        <v>0</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48" s="10">
+        <v>0</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>45574</v>
+      </c>
+      <c r="B49" s="8">
+        <v>0</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D49" s="10">
+        <v>0</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>45512</v>
+      </c>
+      <c r="B50" s="8">
+        <v>0</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50" s="10">
+        <v>0</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>45449</v>
+      </c>
+      <c r="B51" s="8">
+        <v>0</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D51" s="10">
+        <v>0</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
+        <v>45408</v>
+      </c>
+      <c r="B52" s="8">
+        <v>0</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D52" s="10">
+        <v>0</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
+        <v>45398</v>
+      </c>
+      <c r="B53" s="8">
+        <v>0</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="10">
+        <v>0</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/Fundamentals/2025百大牛股/2025年百大牛股.xlsx
+++ b/docs/Fundamentals/2025百大牛股/2025年百大牛股.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\【0#】DeepReview深度复盘\warrenluccie.github.io\docs\Fundamentals\2025百大牛股\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\warrenpyquant\examples\warrenluccie.github.io\docs\Fundamentals\2025百大牛股\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024B06B7-5983-4642-8AE7-861881F4C31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E012791-7006-4D27-BC26-16983F930F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="328" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="954" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="上纬新材 688585" sheetId="1" r:id="rId1"/>
     <sheet name="天普股份 605255" sheetId="2" r:id="rId2"/>
     <sheet name="飞沃科技 301232" sheetId="3" r:id="rId3"/>
+    <sheet name="嘉美包装 002969" sheetId="4" r:id="rId4"/>
+    <sheet name=" ST亚振 603389" sheetId="5" r:id="rId5"/>
+    <sheet name="ST宇顺 002289" sheetId="6" r:id="rId6"/>
+    <sheet name="国晟科技 603778" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="657">
   <si>
     <t>发生日期</t>
   </si>
@@ -812,6 +816,1433 @@
   </si>
   <si>
     <t>公司已用于商业航天项目的产品主要包括商业火箭及火箭发动机所用的紧固件。</t>
+  </si>
+  <si>
+    <t>2593.27万</t>
+  </si>
+  <si>
+    <t>3629.57万</t>
+  </si>
+  <si>
+    <t>1.16亿</t>
+  </si>
+  <si>
+    <t>3.33亿</t>
+  </si>
+  <si>
+    <t>追觅入主+三片罐龙头+饮料灌装</t>
+  </si>
+  <si>
+    <t>1、据2025年12月17日公告，控股股东中国食品包装拟向苏州逐越鸿智协议转让29.9%股份，逐越鸿智同步发起25%股份要约收购，完成后将成为新控股股东，逐越鸿智由追觅科技创始人俞浩控制。 2、据中证报2月7日报道，嘉美包装2月2日复牌。嘉美包装在复牌公告中表示，公司不涉及机器人、扫地机器人相关业务，主营业务仍为食品饮料包装容器的研发、设计、生产和销售及提供饮料灌装服务；公司生产经营未发生重大变化，市场环境或行业政策未发生重大调整；预计未来12个月内，公司主营业务不会发生重大变化。 3、据2025年4月25日年报及2025年10月15日互动易，公司是国内最大金属易拉罐生产商之一，三片罐市占率领先，具备全国最大之一的饮料代工灌装产能，客户覆盖六个核桃、旺旺、王老吉、银鹭、露露、燕京、雪花、青岛等头部品牌。 4、据2025年11月20日互动易，公司5%以上股东富新投资、中凯投资由中国东方100%持有，最终控制人为中央汇金，为中央金融企业。</t>
+  </si>
+  <si>
+    <t>524.44万</t>
+  </si>
+  <si>
+    <t>6826.86万</t>
+  </si>
+  <si>
+    <t>包装印刷+追觅入主+三片罐</t>
+  </si>
+  <si>
+    <t>7155.30万</t>
+  </si>
+  <si>
+    <t>9334.29万</t>
+  </si>
+  <si>
+    <t>控制权变更+追觅关联+饮料灌装</t>
+  </si>
+  <si>
+    <t>1、据2025年12月17日公告，控股股东中国食品包装拟向苏州逐越鸿智协议转让29.9%股份并放弃表决权，逐越鸿智同步发起25%股份要约收购，完成后将成为新控股股东。 2、逐越鸿智是由追觅科技创始人俞浩控制的有限合伙企业。市场预期公司与追觅存在业务协同或资产注入的可能性。 3、据2025年4月25日年报及2025年10月14日互动易，公司是国内最大金属易拉罐生产商之一，三片罐市占率领先，具备全国最大之一的饮料代工灌装产能，客户覆盖六个核桃、旺旺、王老吉、银鹭、露露等头部品牌。</t>
+  </si>
+  <si>
+    <t>2564.78万</t>
+  </si>
+  <si>
+    <t>1.10亿</t>
+  </si>
+  <si>
+    <t>控制权变更+饮料罐装</t>
+  </si>
+  <si>
+    <t>控股股东拟变更为逐越鸿智，追觅科技创始人俞浩将成公司新实控人</t>
+  </si>
+  <si>
+    <t>1.47亿</t>
+  </si>
+  <si>
+    <t>1.80亿</t>
+  </si>
+  <si>
+    <t>控制权变更+三片罐龙头+电商概念</t>
+  </si>
+  <si>
+    <t>1、据2025年12月17日公告，控股股东中国食品包装拟向苏州逐越鸿智协议转让29.9%股份并放弃表决权，逐越鸿智同步发起25%股份要约收购，完成后将成为新控股股东，逐越鸿智由追觅科技创始人俞浩100%持有。 2、据2025年4月25日年报，公司是国内最大金属易拉罐生产商之一，三片罐市占率领先，具备全国最大之一的第三方饮料代工灌装产能。 3、据2025年4月25日年报，公司1L马口铁啤酒罐已批量供应品牌啤酒商，并持续开发精酿啤酒新品，形成“喝吧”自主品牌精酿啤酒电商销售。</t>
+  </si>
+  <si>
+    <t>1.08亿</t>
+  </si>
+  <si>
+    <t>1.18亿</t>
+  </si>
+  <si>
+    <t>1.19亿</t>
+  </si>
+  <si>
+    <t>1.53亿</t>
+  </si>
+  <si>
+    <t>控制权变更+回购贷款</t>
+  </si>
+  <si>
+    <t>1、1月11日晚，嘉美包装披露股票交易停牌核查结果暨复牌公告称，经核查，公司主营业务未发生重大变化，不存在应披露而未披露的重大信息。鉴于相关核查工作已完成，公司股票将于1月12日开市起复牌。 2、据2025年12月17日公告，控股股东中包香港拟向苏州逐越鸿智协议转让29.9%股份并放弃剩余表决权，逐越鸿智同步发起25%股份要约收购，完成后将成为新控股股东。据21世纪经济报道2025年12月19日报道，逐越鸿智的背后，知名家庭及商用机器人企业追觅科技创始人俞浩，通过持有逐越鸿智100%的合伙份额。 3、据2025年4月25日年报，公司是国内最大金属易拉罐生产商之一，三片罐市占率领先，拥有全国最大之一的第三方饮料代工灌装产能。 4、据2024年10月27日取得的中信银行贷款承诺函及2025年4月2日公告，公司已获1.05亿元股票回购专项贷款承诺并已实施1500万元首期贷款用于回购。</t>
+  </si>
+  <si>
+    <t>2.52亿</t>
+  </si>
+  <si>
+    <t>控制权变更+复牌+专项贷款</t>
+  </si>
+  <si>
+    <t>2.54亿</t>
+  </si>
+  <si>
+    <t>4.41亿</t>
+  </si>
+  <si>
+    <t>3853.85万</t>
+  </si>
+  <si>
+    <t>5328.90万</t>
+  </si>
+  <si>
+    <t>包装印刷+控制权变更+海峡西岸</t>
+  </si>
+  <si>
+    <t>1、据2025年12月17日公告，控股股东中包香港拟将所持29.9%股份协议转让给苏州逐越鸿智，并放弃剩余股份表决权；逐越鸿智同步启动25%股份的部分要约收购，交易完成后将成为新控股股东，实际控制人变更为俞浩。 2、据2024年年度报告，公司主营食品饮料金属包装及饮料灌装，三片罐市占率领先，为国内最大金属易拉罐生产商之一，可为客户提供一体化设计、印刷、生产、配送、灌装全流程服务。 3、据2025年10月15日互动易，公司客户覆盖旺旺、王老吉、银鹭、燕京、雪花、青岛等两岸知名饮料及啤酒品牌，市场全覆盖销售目标完成较优。</t>
+  </si>
+  <si>
+    <t>9.40亿</t>
+  </si>
+  <si>
+    <t>4.69亿</t>
+  </si>
+  <si>
+    <t>14.59亿</t>
+  </si>
+  <si>
+    <t>4.42亿</t>
+  </si>
+  <si>
+    <t>14.36亿</t>
+  </si>
+  <si>
+    <t>4.91亿</t>
+  </si>
+  <si>
+    <t>17.09亿</t>
+  </si>
+  <si>
+    <t>4.31亿</t>
+  </si>
+  <si>
+    <t>14.94亿</t>
+  </si>
+  <si>
+    <t>4.48亿</t>
+  </si>
+  <si>
+    <t>16.04亿</t>
+  </si>
+  <si>
+    <t>3.99亿</t>
+  </si>
+  <si>
+    <t>8.72亿</t>
+  </si>
+  <si>
+    <t>4.17亿</t>
+  </si>
+  <si>
+    <t>20.27亿</t>
+  </si>
+  <si>
+    <t>4.51亿</t>
+  </si>
+  <si>
+    <t>13.78亿</t>
+  </si>
+  <si>
+    <t>4.34亿</t>
+  </si>
+  <si>
+    <t>12.19亿</t>
+  </si>
+  <si>
+    <t>4.72亿</t>
+  </si>
+  <si>
+    <t>16.32亿</t>
+  </si>
+  <si>
+    <t>1.16万</t>
+  </si>
+  <si>
+    <t>包装印刷</t>
+  </si>
+  <si>
+    <t>公司所属行业为：包装印刷</t>
+  </si>
+  <si>
+    <t>3856.12万</t>
+  </si>
+  <si>
+    <t>3.08亿</t>
+  </si>
+  <si>
+    <t>包装印刷+三片罐龙头+回购完成</t>
+  </si>
+  <si>
+    <t>1、据2025年4月25日年度报告，公司主营食品饮料金属包装及饮料灌装，三片罐市占率领先，为国内最大金属易拉罐生产商之一，可为客户提供一体化设计、印刷、生产、配送、灌装全流程服务。 2、据2025年10月15日互动易，公司市场全覆盖的销售目标完成较优，公司优势业务与品牌供应链需求契合的业务规模就大。六个核桃、旺旺、王老吉、银鹭食品、露露等头部饮料品牌二十多年来一直稳居前十客户行列。燕京、雪花、青岛等头部啤酒品牌也是公司客户。 3、据2025年11月13日公告，公司累计回购7500万元股份，回购方案已实施完毕，用于可转债转股，回购价不超4.40元/股。 4、据2025年6月5日互动易，公司与瑞幸咖啡的供应商菲诺有合作专供瑞幸门店用原料产品，公司接单工厂已取得瑞幸合格供应商认证。</t>
+  </si>
+  <si>
+    <t>3.04亿</t>
+  </si>
+  <si>
+    <t>《关于增强消费品供需适配性进一步促进消费的实施方案》印发|公司主营食品饮料包装容器</t>
+  </si>
+  <si>
+    <t>4.28亿</t>
+  </si>
+  <si>
+    <t>阿里、美团掀起外卖大战|公司主营食品饮料包装容器</t>
+  </si>
+  <si>
+    <t>879.73万</t>
+  </si>
+  <si>
+    <t>1.57亿</t>
+  </si>
+  <si>
+    <t>包装印刷+啤酒概念</t>
+  </si>
+  <si>
+    <t>港股龙头连续新高；新消费概念火热|公司主营食品饮料包装容器，公司第四大股东公司自有品牌“喝吧”精酿啤酒、咖啡等软饮料</t>
+  </si>
+  <si>
+    <t>4839.71万</t>
+  </si>
+  <si>
+    <t>4.67亿</t>
+  </si>
+  <si>
+    <t>2.91亿</t>
+  </si>
+  <si>
+    <t>发改委：将强化“两新”（消费品以旧换新和大规模设备更新）政策储备|公司主营食品饮料包装容器，公司第四大股东公司自有品牌“喝吧”精酿啤酒、咖啡等软饮料</t>
+  </si>
+  <si>
+    <t>3784.77万</t>
+  </si>
+  <si>
+    <t>1.28亿</t>
+  </si>
+  <si>
+    <t>大消费+活跃小盘非融+业绩预增</t>
+  </si>
+  <si>
+    <t>全国商务工作会议在京召开：推进提振消费专项行动|公司主营食品饮料包装容器，公司第四大股东公司自有品牌“喝吧”精酿啤酒、咖啡等软饮料</t>
+  </si>
+  <si>
+    <t>86.98万</t>
+  </si>
+  <si>
+    <t>1.54亿</t>
+  </si>
+  <si>
+    <t>1.62亿</t>
+  </si>
+  <si>
+    <t>2.04亿</t>
+  </si>
+  <si>
+    <t>2.25亿</t>
+  </si>
+  <si>
+    <t>监管监控+个股调整</t>
+  </si>
+  <si>
+    <t>公告显示，嘉美包装股票自2025年12月17日至2026年2月12日期间累计涨幅高达632.24%，连续多次触发交易异常波动。2月10日至12日三个交易日，公司股票收盘价格涨幅偏离值累计达20.44%，再度触及异常波动标准。公司已先后于2026年1月7日、1月26日实施停牌核查，并分别于1月12日、2月2日公告核查结果复牌。公告明确，若股价继续异常上涨，公司将再次申请停牌核查。同时，深交所已将嘉美包装股票纳入重点监控范围。</t>
+  </si>
+  <si>
+    <t>61.72万</t>
+  </si>
+  <si>
+    <t>2678.04万</t>
+  </si>
+  <si>
+    <t>7681.90万</t>
+  </si>
+  <si>
+    <t>7866.88万</t>
+  </si>
+  <si>
+    <t>500.85万</t>
+  </si>
+  <si>
+    <t>528.62万</t>
+  </si>
+  <si>
+    <t>815.52万</t>
+  </si>
+  <si>
+    <t>1217.71万</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>追觅入主</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三片罐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>饮料灌装</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特斯拉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月或发布新款机器人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>控股股东拟变更为逐越鸿智，追觅科技创始人俞浩将成公司新实控人</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1232.49万</t>
+  </si>
+  <si>
+    <t>2369.29万</t>
+  </si>
+  <si>
+    <t>ST板块</t>
+  </si>
+  <si>
+    <t>公司主要从事中高端海派艺术家具产品的生产</t>
+  </si>
+  <si>
+    <t>681.61万</t>
+  </si>
+  <si>
+    <t>2082.21万</t>
+  </si>
+  <si>
+    <t>旅游概念</t>
+  </si>
+  <si>
+    <t>多只ST股25年业绩有望扭亏|公司主要从事中高端海派艺术家具产品的生产</t>
+  </si>
+  <si>
+    <t>1157.99万</t>
+  </si>
+  <si>
+    <t>682.02万</t>
+  </si>
+  <si>
+    <t>300.15万</t>
+  </si>
+  <si>
+    <t>426.20万</t>
+  </si>
+  <si>
+    <t>51.69万</t>
+  </si>
+  <si>
+    <t>公司于2025-05-06更名为*ST亚振</t>
+  </si>
+  <si>
+    <t>752.08万</t>
+  </si>
+  <si>
+    <t>857.85万</t>
+  </si>
+  <si>
+    <t>939.55万</t>
+  </si>
+  <si>
+    <t>1428.03万</t>
+  </si>
+  <si>
+    <t>145.37万</t>
+  </si>
+  <si>
+    <t>820.23万</t>
+  </si>
+  <si>
+    <t>800.08万</t>
+  </si>
+  <si>
+    <t>3048.05万</t>
+  </si>
+  <si>
+    <t>新零售</t>
+  </si>
+  <si>
+    <t>3996.35万</t>
+  </si>
+  <si>
+    <t>5302.21万</t>
+  </si>
+  <si>
+    <t>2236.68万</t>
+  </si>
+  <si>
+    <t>2316.70万</t>
+  </si>
+  <si>
+    <t>1312.49万</t>
+  </si>
+  <si>
+    <t>3786.03万</t>
+  </si>
+  <si>
+    <t>870.35万</t>
+  </si>
+  <si>
+    <t>1862.74万</t>
+  </si>
+  <si>
+    <t>958.32万</t>
+  </si>
+  <si>
+    <t>1069.63万</t>
+  </si>
+  <si>
+    <t>1595.87万</t>
+  </si>
+  <si>
+    <t>2346.81万</t>
+  </si>
+  <si>
+    <t>308.90万</t>
+  </si>
+  <si>
+    <t>553.74万</t>
+  </si>
+  <si>
+    <t>2783.07万</t>
+  </si>
+  <si>
+    <t>565.42万</t>
+  </si>
+  <si>
+    <t>1089.35万</t>
+  </si>
+  <si>
+    <t>培育钻石</t>
+  </si>
+  <si>
+    <t>699.33万</t>
+  </si>
+  <si>
+    <t>3291.39万</t>
+  </si>
+  <si>
+    <t>2555.28万</t>
+  </si>
+  <si>
+    <t>1681.00万</t>
+  </si>
+  <si>
+    <t>2348.73万</t>
+  </si>
+  <si>
+    <t>1679.11万</t>
+  </si>
+  <si>
+    <t>2941.66万</t>
+  </si>
+  <si>
+    <t>1244.41万</t>
+  </si>
+  <si>
+    <t>2424.51万</t>
+  </si>
+  <si>
+    <t>344.20万</t>
+  </si>
+  <si>
+    <t>1554.44万</t>
+  </si>
+  <si>
+    <t>1036.43万</t>
+  </si>
+  <si>
+    <t>1670.57万</t>
+  </si>
+  <si>
+    <t>1021.71万</t>
+  </si>
+  <si>
+    <t>2374.99万</t>
+  </si>
+  <si>
+    <t>1009.97万</t>
+  </si>
+  <si>
+    <t>1347.37万</t>
+  </si>
+  <si>
+    <t>129.87万</t>
+  </si>
+  <si>
+    <t>156.64万</t>
+  </si>
+  <si>
+    <t>503.85万</t>
+  </si>
+  <si>
+    <t>24.48万</t>
+  </si>
+  <si>
+    <t>36.77万</t>
+  </si>
+  <si>
+    <t>373.80万</t>
+  </si>
+  <si>
+    <t>1380.46万</t>
+  </si>
+  <si>
+    <t>79.93万</t>
+  </si>
+  <si>
+    <t>904.10万</t>
+  </si>
+  <si>
+    <t>4306.64万</t>
+  </si>
+  <si>
+    <t>6655.06万</t>
+  </si>
+  <si>
+    <t>3618.87万</t>
+  </si>
+  <si>
+    <t>4077.47万</t>
+  </si>
+  <si>
+    <t>2702.56万</t>
+  </si>
+  <si>
+    <t>3066.18万</t>
+  </si>
+  <si>
+    <t>2433.79万</t>
+  </si>
+  <si>
+    <t>3692.53万</t>
+  </si>
+  <si>
+    <t>1842.70万</t>
+  </si>
+  <si>
+    <t>3783.98万</t>
+  </si>
+  <si>
+    <t>549.37万</t>
+  </si>
+  <si>
+    <t>936.68万</t>
+  </si>
+  <si>
+    <t>859.22万</t>
+  </si>
+  <si>
+    <t>1641.16万</t>
+  </si>
+  <si>
+    <t>2077.32万</t>
+  </si>
+  <si>
+    <t>645.42万</t>
+  </si>
+  <si>
+    <t>1417.94万</t>
+  </si>
+  <si>
+    <t>7.41万</t>
+  </si>
+  <si>
+    <t>484.60万</t>
+  </si>
+  <si>
+    <t>1050.88万</t>
+  </si>
+  <si>
+    <t>10.38万</t>
+  </si>
+  <si>
+    <t>5431.06万</t>
+  </si>
+  <si>
+    <t>5715.23万</t>
+  </si>
+  <si>
+    <t>1708.25万</t>
+  </si>
+  <si>
+    <t>2244.44万</t>
+  </si>
+  <si>
+    <t>220.12万</t>
+  </si>
+  <si>
+    <t>1181.44万</t>
+  </si>
+  <si>
+    <t>1379.33万</t>
+  </si>
+  <si>
+    <t>1.32亿</t>
+  </si>
+  <si>
+    <t>1.38亿</t>
+  </si>
+  <si>
+    <t>1.05亿</t>
+  </si>
+  <si>
+    <t>1.15亿</t>
+  </si>
+  <si>
+    <t>2.07万</t>
+  </si>
+  <si>
+    <t>1148.67万</t>
+  </si>
+  <si>
+    <t>2528.78万</t>
+  </si>
+  <si>
+    <t>2640.07万</t>
+  </si>
+  <si>
+    <t>3417.22万</t>
+  </si>
+  <si>
+    <t>2227.70万</t>
+  </si>
+  <si>
+    <t>2504.31万</t>
+  </si>
+  <si>
+    <t>8.88万</t>
+  </si>
+  <si>
+    <t>旅游概念</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ST</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>板块</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>218.97万</t>
+  </si>
+  <si>
+    <t>1759.07万</t>
+  </si>
+  <si>
+    <t>算力租赁</t>
+  </si>
+  <si>
+    <t>公司重大资产重组进展顺利，已支付17亿完成资产接管</t>
+  </si>
+  <si>
+    <t>3566.25万</t>
+  </si>
+  <si>
+    <t>2.80万</t>
+  </si>
+  <si>
+    <t>公司于2025-05-06更名为*ST宇顺</t>
+  </si>
+  <si>
+    <t>1485.45万</t>
+  </si>
+  <si>
+    <t>1877.05万</t>
+  </si>
+  <si>
+    <t>969.37万</t>
+  </si>
+  <si>
+    <t>2518.95万</t>
+  </si>
+  <si>
+    <t>0.29万</t>
+  </si>
+  <si>
+    <t>数据中心</t>
+  </si>
+  <si>
+    <t>谷歌云正式官宣涨价 数据中心板块迎来密集利好催化</t>
+  </si>
+  <si>
+    <t>2573.77万</t>
+  </si>
+  <si>
+    <t>2168.31万</t>
+  </si>
+  <si>
+    <t>3675.43万</t>
+  </si>
+  <si>
+    <t>2195.23万</t>
+  </si>
+  <si>
+    <t>2660.51万</t>
+  </si>
+  <si>
+    <t>1396.41万</t>
+  </si>
+  <si>
+    <t>1523.33万</t>
+  </si>
+  <si>
+    <t>306.07万</t>
+  </si>
+  <si>
+    <t>1918.51万</t>
+  </si>
+  <si>
+    <t>1607.14万</t>
+  </si>
+  <si>
+    <t>2970.44万</t>
+  </si>
+  <si>
+    <t>1200.93万</t>
+  </si>
+  <si>
+    <t>2700.84万</t>
+  </si>
+  <si>
+    <t>公司拟购买3家公司100%股权，交易总对价33.5亿元</t>
+  </si>
+  <si>
+    <t>284.48万</t>
+  </si>
+  <si>
+    <t>2683.19万</t>
+  </si>
+  <si>
+    <t>213.32万</t>
+  </si>
+  <si>
+    <t>1935.19万</t>
+  </si>
+  <si>
+    <t>1073.60万</t>
+  </si>
+  <si>
+    <t>14.93万</t>
+  </si>
+  <si>
+    <t>155.99万</t>
+  </si>
+  <si>
+    <t>2187.90万</t>
+  </si>
+  <si>
+    <t>1889.07万</t>
+  </si>
+  <si>
+    <t>1014.44万</t>
+  </si>
+  <si>
+    <t>2583.92万</t>
+  </si>
+  <si>
+    <t>1724.55万</t>
+  </si>
+  <si>
+    <t>618.45万</t>
+  </si>
+  <si>
+    <t>243.73万</t>
+  </si>
+  <si>
+    <t>1544.99万</t>
+  </si>
+  <si>
+    <t>1139.74万</t>
+  </si>
+  <si>
+    <t>600.54万</t>
+  </si>
+  <si>
+    <t>1624.57万</t>
+  </si>
+  <si>
+    <t>577.87万</t>
+  </si>
+  <si>
+    <t>937.81万</t>
+  </si>
+  <si>
+    <t>260.15万</t>
+  </si>
+  <si>
+    <t>2155.49万</t>
+  </si>
+  <si>
+    <t>1472.11万</t>
+  </si>
+  <si>
+    <t>2311.52万</t>
+  </si>
+  <si>
+    <t>352.17万</t>
+  </si>
+  <si>
+    <t>1513.21万</t>
+  </si>
+  <si>
+    <t>1164.40万</t>
+  </si>
+  <si>
+    <t>1433.96万</t>
+  </si>
+  <si>
+    <t>859.78万</t>
+  </si>
+  <si>
+    <t>238.44万</t>
+  </si>
+  <si>
+    <t>344.79万</t>
+  </si>
+  <si>
+    <t>73.78万</t>
+  </si>
+  <si>
+    <t>80.39万</t>
+  </si>
+  <si>
+    <t>2183.23万</t>
+  </si>
+  <si>
+    <t>7871.30万</t>
+  </si>
+  <si>
+    <t>1.21亿</t>
+  </si>
+  <si>
+    <t>1.26亿</t>
+  </si>
+  <si>
+    <t>7119.64万</t>
+  </si>
+  <si>
+    <t>7682.06万</t>
+  </si>
+  <si>
+    <t>391.79万</t>
+  </si>
+  <si>
+    <t>1.34亿</t>
+  </si>
+  <si>
+    <t>1.11亿</t>
+  </si>
+  <si>
+    <t>3083.33万</t>
+  </si>
+  <si>
+    <t>3346.99万</t>
+  </si>
+  <si>
+    <t>1548.85万</t>
+  </si>
+  <si>
+    <t>2754.20万</t>
+  </si>
+  <si>
+    <t>323.27万</t>
+  </si>
+  <si>
+    <t>108.19万</t>
+  </si>
+  <si>
+    <t>210.12万</t>
+  </si>
+  <si>
+    <t>93.70万</t>
+  </si>
+  <si>
+    <t>1069.99万</t>
+  </si>
+  <si>
+    <t>1953.29万</t>
+  </si>
+  <si>
+    <t>1968.77万</t>
+  </si>
+  <si>
+    <t>2564.05万</t>
+  </si>
+  <si>
+    <t>236.73万</t>
+  </si>
+  <si>
+    <t>2914.18万</t>
+  </si>
+  <si>
+    <t>7205.64万</t>
+  </si>
+  <si>
+    <t>7637.67万</t>
+  </si>
+  <si>
+    <t>1024.19万</t>
+  </si>
+  <si>
+    <t>144.12万</t>
+  </si>
+  <si>
+    <t>340.03万</t>
+  </si>
+  <si>
+    <t>416.10万</t>
+  </si>
+  <si>
+    <t>59.50万</t>
+  </si>
+  <si>
+    <t>6301.88万</t>
+  </si>
+  <si>
+    <t>11.11万</t>
+  </si>
+  <si>
+    <t>481.41万</t>
+  </si>
+  <si>
+    <t>418.76万</t>
+  </si>
+  <si>
+    <t>1074.98万</t>
+  </si>
+  <si>
+    <t>4477.40万</t>
+  </si>
+  <si>
+    <t>2.11亿</t>
+  </si>
+  <si>
+    <t>储能+固态电池+光伏</t>
+  </si>
+  <si>
+    <t>特斯拉计划采购中国光伏设备|全球前三大异质结产品制造商；消息称公司近期成功为某商业航天公司6U立方卫星提供HJT光伏系统，单星输出功率15W，较砷化镓方案效率提升18%、重量减轻25%，且已稳定运行超1年</t>
+  </si>
+  <si>
+    <t>1287.84万</t>
+  </si>
+  <si>
+    <t>1.45亿</t>
+  </si>
+  <si>
+    <t>光伏设备+固态电池+异质结光伏</t>
+  </si>
+  <si>
+    <t>英伟达发布"太空计算"平台|全球前三大异质结产品制造商；消息称公司近期成功为某商业航天公司6U立方卫星提供HJT光伏系统，单星输出功率15W，较砷化镓方案效率提升18%、重量减轻25%，且已稳定运行超1年</t>
+  </si>
+  <si>
+    <t>1.03亿</t>
+  </si>
+  <si>
+    <t>4.07亿</t>
+  </si>
+  <si>
+    <t>固态电池+光伏设备+光伏治沙</t>
+  </si>
+  <si>
+    <t>光伏组件价格出现实质性上调|全球前三大异质结产品制造商；消息称公司近期成功为某商业航天公司6U立方卫星提供HJT光伏系统，单星输出功率15W，较砷化镓方案效率提升18%、重量减轻25%，且已稳定运行超1年</t>
+  </si>
+  <si>
+    <t>1215.68万</t>
+  </si>
+  <si>
+    <t>4.77亿</t>
+  </si>
+  <si>
+    <t>固态电池+储能+虚拟电厂</t>
+  </si>
+  <si>
+    <t>7797.88万</t>
+  </si>
+  <si>
+    <t>5.20亿</t>
+  </si>
+  <si>
+    <t>光伏设备+固态电池</t>
+  </si>
+  <si>
+    <t>1、据2025年10月14日公告并于2026年2月5日异常波动公告再次提示，二级控股子公司安徽国晟新能源拟以2.3亿元增资铁岭环球，投建固态电池产业链智能制造项目。 2、据2025年4月26日年报，公司主营大尺寸高效异质结HJT光伏电池及组件，已在江苏、安徽、山东、新疆等地完成从切片到电池、组件的垂直生态产业链布局。 3、据2026年3月4日人民财讯报道，公司与合作方成立国晟炬能江苏新能源科技有限公司，经营范围含人工智能应用软件开发、碳减排技术研发等。</t>
+  </si>
+  <si>
+    <t>2204.28万</t>
+  </si>
+  <si>
+    <t>2.62亿</t>
+  </si>
+  <si>
+    <t>光伏设备+固态电池+储能</t>
+  </si>
+  <si>
+    <t>全球前三大异质结产品制造商；消息称公司近期成功为某商业航天公司6U立方卫星提供HJT光伏系统，单星输出功率15W，较砷化镓方案效率提升18%、重量减轻25%，且已稳定运行超1年</t>
+  </si>
+  <si>
+    <t>8840.11万</t>
+  </si>
+  <si>
+    <t>光伏设备+固态电池+钙钛矿</t>
+  </si>
+  <si>
+    <t>SpaceX收购xAI，总估值达1.25万亿美元|1、据2025年8月27日半年报，公司主营大尺寸高效异质结光伏电池及组件，拥有78项光伏专利，产品通过CQC、TUV等认证。 2、据2025年10月14日公告，二级控股子公司安徽国晟新能源拟2.3亿元增资铁岭环球投建固态电池产业链项目，布局新能源电池赛道。 3、据2024年年报，公司以光伏新型能源和生态园林为“双主业”，并在江苏、安徽、山东、新疆等地完成垂直产业链布局。</t>
+  </si>
+  <si>
+    <t>6645.98万</t>
+  </si>
+  <si>
+    <t>5839.56万</t>
+  </si>
+  <si>
+    <t>6993.82万</t>
+  </si>
+  <si>
+    <t>固态电池+光伏组件</t>
+  </si>
+  <si>
+    <t>1、据2026年1月22日快讯，国晟科技午后打开跌停，终结此前连续5个交易日跌停。 2、据2025年8月27日半年报，公司主营大尺寸高效异质结光伏电池及组件，拥有87项光伏专利，产品通过CQC、TUV等认证，客户含中广核等能源集团。 3、据2025年10月14日公告，二级控股子公司安徽国晟新能源拟2.3亿元增资铁岭环球投建固态电池产业链项目，布局新能源电池赛道。</t>
+  </si>
+  <si>
+    <t>5970.61万</t>
+  </si>
+  <si>
+    <t>光伏设备+固态电池+孚悦科技</t>
+  </si>
+  <si>
+    <t>1、据2025年10月14日公告，公司二级控股子公司安徽国晟新能源拟以2.3亿元增资铁岭环球，投建年产10GWh固态电池产业链AI智能制造项目，产品配套具身智能、低空经济等前沿场景并已签署3份国内及1份国际销售意向协议。 2、据2025年11月29日公告，公司拟以2.406亿元收购孚悦科技100%股权，标的专注高精密度锂电池结构件，交易完成后将强化新能源电池供应链整合。 3、据2025年8月27日半年报及2025年9月11日机构调研，公司“光伏+园林”双主业成型，光伏业务覆盖大尺寸高效异质结电池及组件，徐州、淮北、淮南、新疆基地已投产，山东基地完成调试，垂直生态产业链布局基本形成。</t>
+  </si>
+  <si>
+    <t>8553.59万</t>
+  </si>
+  <si>
+    <t>8921.44万</t>
+  </si>
+  <si>
+    <t>固态电池+光伏设备+孚悦科技</t>
+  </si>
+  <si>
+    <t>8382.40万</t>
+  </si>
+  <si>
+    <t>8964.10万</t>
+  </si>
+  <si>
+    <t>1、全球前三大异质结产品制造商；公司聚焦大尺寸高效异质结电池、组件研发生产及光伏电站 EPC 业务，布局多生产基地形成垂直产业链，产品适配多元场景； 2、子公司拟2.3亿元增资铁岭环球，后者拟投资年产10GWh固态电池产业链AI智能制造项目； 3、公司拟2.406亿元收购孚悦科技100%股权，标的公司主要从事高精密度新型锂电池结构件的研产销</t>
+  </si>
+  <si>
+    <t>3338.25万</t>
+  </si>
+  <si>
+    <t>5739.08万</t>
+  </si>
+  <si>
+    <t>2353.56万</t>
+  </si>
+  <si>
+    <t>3733.72万</t>
+  </si>
+  <si>
+    <t>光伏设备+固体电池+钙钛矿电池</t>
+  </si>
+  <si>
+    <t>市场监管总局开展规范光伏行业价格竞争秩序合规指导；四家头部硅片企业联合大幅上调报价|1、全球前三大异质结产品制造商；公司聚焦大尺寸高效异质结电池、组件研发生产及光伏电站 EPC 业务，布局多生产基地形成垂直产业链，产品适配多元场景； 2、子公司拟2.3亿元增资铁岭环球，后者拟投资年产10GWh固态电池产业链AI智能制造项目； 3、公司拟2.406亿元收购孚悦科技100%股权，标的公司主要从事高精密度新型锂电池结构件的研产销</t>
+  </si>
+  <si>
+    <t>3700.08万</t>
+  </si>
+  <si>
+    <t>光伏设备</t>
+  </si>
+  <si>
+    <t>1、公司拟2.406亿元收购孚悦科技100%股权，标的公司主要从事高精密度新型锂电池结构件的研产销； 2、子公司拟2.3亿元增资铁岭环球，后者拟投资年产10GWh固态电池产业链AI智能制造项目； 3、全球前三大异质结产品制造商；公司聚焦大尺寸高效异质结电池、组件研发生产及光伏电站 EPC 业务，布局多生产基地形成垂直产业链，产品适配多元场景</t>
+  </si>
+  <si>
+    <t>5369.15万</t>
+  </si>
+  <si>
+    <t>6146.77万</t>
+  </si>
+  <si>
+    <t>碳酸锂近半年涨价超60%|1、公司拟2.406亿元收购孚悦科技100%股权，标的公司主要从事高精密度新型锂电池结构件的研产销； 2、子公司拟2.3亿元增资铁岭环球，后者拟投资年产10GWh固态电池产业链AI智能制造项目； 3、全球前三大异质结产品制造商；公司聚焦大尺寸高效异质结电池、组件研发生产及光伏电站 EPC 业务，布局多生产基地形成垂直产业链，产品适配多元场景</t>
+  </si>
+  <si>
+    <t>6576.28万</t>
+  </si>
+  <si>
+    <t>1、据2025年11月25日晚间公告，公司拟以2.41亿元收购孚悦科技100%股权，标的主营高精密度新型锂电池结构件，2025年1-8月营收7483.49万元、净利1009.1万元。 2、据2025年10月14日晚间公告，公司二级控股子公司安徽国晟新能源拟以2.3亿元增资铁岭环球，后续由铁岭环球投资建设年产10GWh固态电池产业链AI智能制造项目。 3、据2025年8月27日半年报，公司形成“光伏+园林”双主业，光伏业务覆盖大尺寸高效异质结电池及组件、光伏电站EPC，徐州、淮北、淮南、新疆等基地已投产，山东基地完成调试。</t>
+  </si>
+  <si>
+    <t>2.36亿</t>
+  </si>
+  <si>
+    <t>9712.27万</t>
+  </si>
+  <si>
+    <t>光伏设备+固态电池+10GWh项目</t>
+  </si>
+  <si>
+    <t>有机硅行业实控人会议将在11月18日召开，或将确定减产目标|1、据2025年10月15日公告，公司二级控股子公司安徽国晟新能源拟以2.3亿元增资铁岭环球，后续投资建设固态电池产业链AI智能制造项目。 2、据2025年6月21日公告，安徽国晟新能源与中广核风电签订10.425亿元光伏组件框架采购合同，合同有效期至2025年12月31日，预计将对2025年度及后续业绩产生积极影响。 3、据2025年8月27日半年报，公司形成“光伏+园林”双主业，光伏业务覆盖大尺寸高效异质结电池及组件、光伏电站EPC，园林业务聚焦生态修复、水系治理等生态治理项目。 4、据2025年8月27日半年报，公司徐州、淮北、淮南、新疆等基地均已建成投产，山东基地完成调试并实现首件下线，垂直生态产业链布局基本形成。</t>
+  </si>
+  <si>
+    <t>9112.71万</t>
+  </si>
+  <si>
+    <t>1.84亿</t>
+  </si>
+  <si>
+    <t>3826.89万</t>
+  </si>
+  <si>
+    <t>4976.38万</t>
+  </si>
+  <si>
+    <t>1.81亿</t>
+  </si>
+  <si>
+    <t>有机硅行业实控人会议将在11月18日召开，或将确定减产目标|1、据2025年10月15日公告，公司二级控股子公司安徽国晟新能源拟以2.3亿元增资铁岭环球，后续投资建设年产10GWh固态电池产业链AI智能制造项目，项目已备案并取得相关知识产权许可。 2、据2025年6月21日公告，安徽国晟新能源与中广核风电签订10.43亿元光伏组件框架采购合同，合同有效期至2025年12月31日，预计将对2025年度及后续业绩产生积极影响。 3、据2025年8月27日半年报，公司形成“光伏+园林”双主业，光伏业务覆盖大尺寸高效异质结电池及组件、光伏电站EPC，园林业务聚焦生态修复、水系治理等生态治理项目。 4、据2025年8月27日半年报，公司徐州、淮北、淮南、新疆等基地均已建成投产，山东基地完成调试并实现首件下线，垂直生态产业链布局基本形成。</t>
+  </si>
+  <si>
+    <t>0.35万</t>
+  </si>
+  <si>
+    <t>1、据2025年10月15日披露，公司二级控股子公司安徽国晟新能源拟以23,000万元增资铁岭环球并持股51.11%，后续拟投资建设固态电池产业链AI智能制造项目尚需股东会审议，产品植入AI高智能BMS核心模块，并已签署3份国内及1份国际销售意向协议。 2、据2025年6月21日公告，安徽国晟新能源与中广核风电签订10.43亿元光伏组件框架采购合同，合同有效期至2025年12月31日，预计将对2025年度及后续业绩产生积极影响。 3、据2025年8月27日半年报，公司形成“光伏+园林”双主业，光伏业务覆盖大尺寸高效异质结电池及组件、光伏电站EPC，园林业务聚焦生态修复、水系治理等生态治理项目。 4、据2025年8月27日半年报，公司徐州、淮北、淮南、新疆等基地均已建成投产，山东基地完成调试并实现首件下线，垂直生态产业链布局基本形成。</t>
+  </si>
+  <si>
+    <t>6060.33万</t>
+  </si>
+  <si>
+    <t>2.17亿</t>
+  </si>
+  <si>
+    <t>发改委、能源局发布关于促进新能源消纳和调控的指导意见|1、全球前三大异质结产品制造商；公司聚焦大尺寸高效异质结电池、组件研发生产及光伏电站 EPC 业务，布局多生产基地形成垂直产业链，产品适配多元场景； 2、子公司拟2.3亿元增资铁岭环球，后者拟投资年产10GWh固态电池产业链AI智能制造项目</t>
+  </si>
+  <si>
+    <t>3496.43万</t>
+  </si>
+  <si>
+    <t>1.35亿</t>
+  </si>
+  <si>
+    <t>电解液、六氟磷酸锂价格持续上涨|子公司拟2.3亿元增资铁岭环球，后者拟投资年产10GWh固态电池产业链AI智能制造项目</t>
+  </si>
+  <si>
+    <t>4.85亿</t>
+  </si>
+  <si>
+    <t>9942.71万</t>
+  </si>
+  <si>
+    <t>6051.81万</t>
+  </si>
+  <si>
+    <t>1.73亿</t>
+  </si>
+  <si>
+    <t>4057.46万</t>
+  </si>
+  <si>
+    <t>2.48亿</t>
+  </si>
+  <si>
+    <t>光伏设备+固态电池+10亿订单</t>
+  </si>
+  <si>
+    <t>1、据2025年10月15日披露并于10月17日公告，公司二级控股子公司安徽国晟新能源拟以2.3亿元增资铁岭环球并持股51.11%，后者拟投资建设固态电池产业链AI智能制造项目，项目存在延期、变更或终止风险。 2、据2025年6月21日公告，安徽国晟新能源与中广核风电签订10.43亿元光伏组件框架采购合同，合同有效期至2025年12月31日。 3、据2025年8月27日半年报，公司已形成“光伏+园林”双主业，光伏业务覆盖大尺寸高效异质结电池及组件、光伏电站EPC，园林业务聚焦生态修复、水系治理等生态治理项目。</t>
+  </si>
+  <si>
+    <t>6008.65万</t>
+  </si>
+  <si>
+    <t>六氟磷酸锂节后迎来涨价潮|子公司拟2.3亿元增资铁岭环球，后者拟投资年产10GWh固态电池产业链AI智能制造项目</t>
+  </si>
+  <si>
+    <t>331.89万</t>
+  </si>
+  <si>
+    <t>68.00万</t>
+  </si>
+  <si>
+    <t>520.23万</t>
+  </si>
+  <si>
+    <t>72.97万</t>
+  </si>
+  <si>
+    <t>0.97万</t>
+  </si>
+  <si>
+    <t>15.53亿</t>
+  </si>
+  <si>
+    <t>20.20亿</t>
+  </si>
+  <si>
+    <t>11.96亿</t>
+  </si>
+  <si>
+    <t>13.62亿</t>
+  </si>
+  <si>
+    <t>10.66亿</t>
+  </si>
+  <si>
+    <t>12.01亿</t>
+  </si>
+  <si>
+    <t>9.38亿</t>
+  </si>
+  <si>
+    <t>10.06亿</t>
+  </si>
+  <si>
+    <t>6.16亿</t>
+  </si>
+  <si>
+    <t>3.17万</t>
+  </si>
+  <si>
+    <t>严重异常波动+业绩亏损+商誉风险</t>
+  </si>
+  <si>
+    <t>1、据2025年12月12日严重异常波动公告，公司股票连续30个交易日涨幅偏离值累计达200%，市净率11.68倍显著高于行业3.18倍，存在非理性炒作及短期快速回落风险。 2、据2025年10月30日披露的2025年第三季度报告，公司前三季度归母净利润-1.51亿元，扣非净利润-1.52亿元，业绩持续亏损。 3、据2025年12月12日公告，拟对外投资及收购事项预计形成约2.2亿元商誉，存在减值风险。</t>
+  </si>
+  <si>
+    <t>6543.58万</t>
+  </si>
+  <si>
+    <t>5403.27万</t>
+  </si>
+  <si>
+    <t>5483.73万</t>
+  </si>
+  <si>
+    <t>19.13万</t>
+  </si>
+  <si>
+    <t>1766.46万</t>
+  </si>
+  <si>
+    <t>2141.45万</t>
+  </si>
+  <si>
+    <t>5.83万</t>
+  </si>
+  <si>
+    <t>2620.67万</t>
+  </si>
+  <si>
+    <t>6804.16万</t>
+  </si>
+  <si>
+    <t>316.22万</t>
+  </si>
+  <si>
+    <t>346.99万</t>
+  </si>
+  <si>
+    <t>17.50万</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>光伏设备</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>固态电池</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钙钛矿</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>光伏设备</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>固态电池</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>储能</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -902,7 +2333,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -949,11 +2380,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1002,6 +2448,31 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3661,7 +5132,7 @@
     <col min="7" max="7" width="255.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>5</v>
       </c>
@@ -4403,7 +5874,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>62</v>
       </c>
@@ -4804,4 +6275,5307 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F78E2396-AFF4-4E7F-A846-39A8158DA4FC}">
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="139.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B5" s="23">
+        <v>0.62211805555555555</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B6" s="23">
+        <v>0.40284722222222225</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="22">
+        <v>46063</v>
+      </c>
+      <c r="B7" s="23">
+        <v>0.57621527777777781</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="22">
+        <v>46058</v>
+      </c>
+      <c r="B8" s="23">
+        <v>0.60239583333333335</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="22">
+        <v>46044</v>
+      </c>
+      <c r="B9" s="23">
+        <v>0.40232638888888889</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="22">
+        <v>46042</v>
+      </c>
+      <c r="B10" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="22">
+        <v>46041</v>
+      </c>
+      <c r="B11" s="23">
+        <v>0.39697916666666666</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="22">
+        <v>46036</v>
+      </c>
+      <c r="B12" s="23">
+        <v>0.39753472222222225</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="22">
+        <v>46035</v>
+      </c>
+      <c r="B13" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="25">
+        <v>0</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="22">
+        <v>46034</v>
+      </c>
+      <c r="B14" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="22">
+        <v>46028</v>
+      </c>
+      <c r="B15" s="23">
+        <v>0.41010416666666666</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="22">
+        <v>46022</v>
+      </c>
+      <c r="B16" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="25">
+        <v>0</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="22">
+        <v>46021</v>
+      </c>
+      <c r="B17" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="22">
+        <v>46020</v>
+      </c>
+      <c r="B18" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="22">
+        <v>46017</v>
+      </c>
+      <c r="B19" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="22">
+        <v>46016</v>
+      </c>
+      <c r="B20" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="22">
+        <v>46015</v>
+      </c>
+      <c r="B21" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="22">
+        <v>46014</v>
+      </c>
+      <c r="B22" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="22">
+        <v>46013</v>
+      </c>
+      <c r="B23" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="22">
+        <v>46010</v>
+      </c>
+      <c r="B24" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="22">
+        <v>46009</v>
+      </c>
+      <c r="B25" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="22">
+        <v>46008</v>
+      </c>
+      <c r="B26" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="22">
+        <v>46000</v>
+      </c>
+      <c r="B27" s="23">
+        <v>0.3984375</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="25">
+        <v>0</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="22">
+        <v>45996</v>
+      </c>
+      <c r="B28" s="23">
+        <v>0.54333333333333333</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="22">
+        <v>45993</v>
+      </c>
+      <c r="B29" s="23">
+        <v>0.54822916666666666</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="25">
+        <v>0</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="22">
+        <v>45846</v>
+      </c>
+      <c r="B30" s="23">
+        <v>0.39635416666666667</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="25">
+        <v>0</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="F30" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="22">
+        <v>45813</v>
+      </c>
+      <c r="B31" s="23">
+        <v>0.39604166666666668</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="22">
+        <v>45812</v>
+      </c>
+      <c r="B32" s="23">
+        <v>0.44614583333333335</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="F32" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="22">
+        <v>45804</v>
+      </c>
+      <c r="B33" s="23">
+        <v>0.39673611111111112</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="25">
+        <v>0</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="22">
+        <v>45671</v>
+      </c>
+      <c r="B34" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="F34" s="24" t="s">
+        <v>320</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="20"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B39" s="23">
+        <v>0.61447916666666669</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="25">
+        <v>0</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B40" s="23">
+        <v>0.41312500000000002</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="22">
+        <v>46078</v>
+      </c>
+      <c r="B41" s="23">
+        <v>0.42670138888888887</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="25">
+        <v>0</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="22">
+        <v>46066</v>
+      </c>
+      <c r="B42" s="23">
+        <v>0.43767361111111114</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="G42" s="24" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="22">
+        <v>46055</v>
+      </c>
+      <c r="B43" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="25">
+        <v>0</v>
+      </c>
+      <c r="E43" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="22">
+        <v>46038</v>
+      </c>
+      <c r="B44" s="23">
+        <v>0.43708333333333332</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="F44" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G44" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="22">
+        <v>46037</v>
+      </c>
+      <c r="B45" s="23">
+        <v>0.47479166666666667</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G45" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="22">
+        <v>45754</v>
+      </c>
+      <c r="B46" s="23">
+        <v>0.40986111111111112</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="22">
+        <v>45398</v>
+      </c>
+      <c r="B47" s="23">
+        <v>0.4128472222222222</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>335</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G47" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651421E1-6676-4F29-B94F-5209BDD586EC}">
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="3" max="3" width="20.25" customWidth="1"/>
+    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="5" max="5" width="25.75" customWidth="1"/>
+    <col min="6" max="6" width="23.875" customWidth="1"/>
+    <col min="7" max="7" width="78.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>46077</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.41046296296296297</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>46065</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.43160879629629628</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>46043</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0.41620370370370369</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>46038</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0.61442129629629627</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>46034</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.61711805555555554</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>46027</v>
+      </c>
+      <c r="B10" s="8">
+        <v>0.39681712962962962</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>46021</v>
+      </c>
+      <c r="B11" s="8">
+        <v>0.62503472222222223</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>46017</v>
+      </c>
+      <c r="B12" s="8">
+        <v>0.39993055555555557</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>46016</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0.39954861111111112</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>46015</v>
+      </c>
+      <c r="B14" s="8">
+        <v>0.4294675925925926</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>46010</v>
+      </c>
+      <c r="B15" s="8">
+        <v>0.3923726851851852</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>46009</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0.39239583333333333</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>46008</v>
+      </c>
+      <c r="B17" s="8">
+        <v>0.56873842592592594</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>45993</v>
+      </c>
+      <c r="B18" s="8">
+        <v>0.39240740740740743</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>45972</v>
+      </c>
+      <c r="B19" s="8">
+        <v>0.5659953703703704</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>45966</v>
+      </c>
+      <c r="B20" s="8">
+        <v>0.45177083333333334</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>45965</v>
+      </c>
+      <c r="B21" s="8">
+        <v>0.44091435185185185</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>45957</v>
+      </c>
+      <c r="B22" s="8">
+        <v>0.42126157407407405</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>45954</v>
+      </c>
+      <c r="B23" s="8">
+        <v>0.43230324074074072</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>45952</v>
+      </c>
+      <c r="B24" s="8">
+        <v>0.60184027777777782</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>45951</v>
+      </c>
+      <c r="B25" s="8">
+        <v>0.39645833333333336</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>45946</v>
+      </c>
+      <c r="B26" s="8">
+        <v>0.40475694444444443</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>45945</v>
+      </c>
+      <c r="B27" s="8">
+        <v>0.39238425925925924</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>45944</v>
+      </c>
+      <c r="B28" s="8">
+        <v>0.39238425925925924</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>45943</v>
+      </c>
+      <c r="B29" s="8">
+        <v>0.41702546296296295</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>45930</v>
+      </c>
+      <c r="B30" s="8">
+        <v>0.5783449074074074</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="10">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>45929</v>
+      </c>
+      <c r="B31" s="8">
+        <v>0.40488425925925925</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="10">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>45926</v>
+      </c>
+      <c r="B32" s="8">
+        <v>0.6007986111111111</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>45924</v>
+      </c>
+      <c r="B33" s="8">
+        <v>0.39719907407407407</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>45922</v>
+      </c>
+      <c r="B34" s="8">
+        <v>0.39240740740740743</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B39" s="4">
+        <v>0.43383101851851852</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B40" s="8">
+        <v>0.5794907407407407</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B41" s="8">
+        <v>0.41719907407407408</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="10">
+        <v>0</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>46056</v>
+      </c>
+      <c r="B42" s="8">
+        <v>0.55457175925925928</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>46031</v>
+      </c>
+      <c r="B43" s="8">
+        <v>0.40707175925925926</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="10">
+        <v>0</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>46022</v>
+      </c>
+      <c r="B44" s="8">
+        <v>0.59166666666666667</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>46007</v>
+      </c>
+      <c r="B45" s="8">
+        <v>0.39238425925925924</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>46006</v>
+      </c>
+      <c r="B46" s="8">
+        <v>0.39239583333333333</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>46003</v>
+      </c>
+      <c r="B47" s="8">
+        <v>0.39239583333333333</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>46002</v>
+      </c>
+      <c r="B48" s="8">
+        <v>0.39238425925925924</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>46001</v>
+      </c>
+      <c r="B49" s="8">
+        <v>0.39710648148148148</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>45992</v>
+      </c>
+      <c r="B50" s="8">
+        <v>0.58718749999999997</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>45989</v>
+      </c>
+      <c r="B51" s="8">
+        <v>0.40333333333333332</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="10">
+        <v>0</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
+        <v>45988</v>
+      </c>
+      <c r="B52" s="8">
+        <v>0.40329861111111109</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
+        <v>45987</v>
+      </c>
+      <c r="B53" s="8">
+        <v>0.41062500000000002</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="7">
+        <v>45979</v>
+      </c>
+      <c r="B54" s="8">
+        <v>0.44032407407407409</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="10">
+        <v>0</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
+        <v>45978</v>
+      </c>
+      <c r="B55" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="7">
+        <v>45974</v>
+      </c>
+      <c r="B56" s="8">
+        <v>0.4012384259259259</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" s="10">
+        <v>0</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="7">
+        <v>45973</v>
+      </c>
+      <c r="B57" s="8">
+        <v>0.43734953703703705</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="7">
+        <v>45964</v>
+      </c>
+      <c r="B58" s="8">
+        <v>0.39239583333333333</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="7">
+        <v>45961</v>
+      </c>
+      <c r="B59" s="8">
+        <v>0.39239583333333333</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="7">
+        <v>45959</v>
+      </c>
+      <c r="B60" s="8">
+        <v>0.41761574074074076</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" s="10">
+        <v>0</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="7">
+        <v>45950</v>
+      </c>
+      <c r="B61" s="8">
+        <v>0.39240740740740743</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="7">
+        <v>45947</v>
+      </c>
+      <c r="B62" s="8">
+        <v>0.3923726851851852</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
+        <v>45940</v>
+      </c>
+      <c r="B63" s="8">
+        <v>0.41847222222222225</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="10">
+        <v>0</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="7">
+        <v>45939</v>
+      </c>
+      <c r="B64" s="8">
+        <v>0.60100694444444447</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" s="10">
+        <v>0</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
+        <v>45923</v>
+      </c>
+      <c r="B65" s="8">
+        <v>0.43908564814814816</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65" s="10">
+        <v>0</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7">
+        <v>45905</v>
+      </c>
+      <c r="B66" s="8">
+        <v>0.39240740740740743</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
+        <v>45904</v>
+      </c>
+      <c r="B67" s="8">
+        <v>0.39725694444444443</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7">
+        <v>45902</v>
+      </c>
+      <c r="B68" s="8">
+        <v>0.45643518518518517</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EEDF1B7-7C8A-445E-919E-A75D928AD4DF}">
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5" customWidth="1"/>
+    <col min="6" max="6" width="41.125" customWidth="1"/>
+    <col min="7" max="7" width="50.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="22">
+        <v>46105</v>
+      </c>
+      <c r="B5" s="23">
+        <v>0.42503472222222222</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>448</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>449</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B6" s="23">
+        <v>0.55385416666666665</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="25">
+        <v>0</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>452</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="22">
+        <v>46077</v>
+      </c>
+      <c r="B7" s="23">
+        <v>0.625</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="25">
+        <v>0</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>453</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="22">
+        <v>46066</v>
+      </c>
+      <c r="B8" s="23">
+        <v>0.47385416666666669</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>456</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="22">
+        <v>46057</v>
+      </c>
+      <c r="B9" s="23">
+        <v>0.60003472222222221</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>457</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="22">
+        <v>46050</v>
+      </c>
+      <c r="B10" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="25">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="22">
+        <v>46043</v>
+      </c>
+      <c r="B11" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="25">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>462</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="22">
+        <v>46042</v>
+      </c>
+      <c r="B12" s="23">
+        <v>0.40944444444444444</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>463</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>464</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="22">
+        <v>46029</v>
+      </c>
+      <c r="B13" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>466</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="22">
+        <v>46028</v>
+      </c>
+      <c r="B14" s="23">
+        <v>0.44388888888888889</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="22">
+        <v>46017</v>
+      </c>
+      <c r="B15" s="23">
+        <v>0.39635416666666667</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>470</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="22">
+        <v>46016</v>
+      </c>
+      <c r="B16" s="23">
+        <v>0.39711805555555557</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>471</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="22">
+        <v>46015</v>
+      </c>
+      <c r="B17" s="23">
+        <v>0.3971527777777778</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>473</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="22">
+        <v>46014</v>
+      </c>
+      <c r="B18" s="23">
+        <v>0.40270833333333333</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>477</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="22">
+        <v>46013</v>
+      </c>
+      <c r="B19" s="23">
+        <v>0.45940972222222221</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>478</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>479</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="22">
+        <v>46009</v>
+      </c>
+      <c r="B20" s="23">
+        <v>0.39815972222222223</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="25">
+        <v>0</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>480</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="22">
+        <v>45986</v>
+      </c>
+      <c r="B21" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="25">
+        <v>0</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>481</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="22">
+        <v>45980</v>
+      </c>
+      <c r="B22" s="23">
+        <v>0.45708333333333334</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>482</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>483</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="22">
+        <v>45966</v>
+      </c>
+      <c r="B23" s="23">
+        <v>0.39618055555555554</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="25">
+        <v>0</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>484</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="22">
+        <v>45965</v>
+      </c>
+      <c r="B24" s="23">
+        <v>0.39993055555555557</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="22">
+        <v>45945</v>
+      </c>
+      <c r="B25" s="23">
+        <v>0.46135416666666668</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="25">
+        <v>0</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="22">
+        <v>45943</v>
+      </c>
+      <c r="B26" s="23">
+        <v>0.42878472222222225</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="25">
+        <v>0</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="22">
+        <v>45926</v>
+      </c>
+      <c r="B27" s="23">
+        <v>0.46</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>489</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>490</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="22">
+        <v>45918</v>
+      </c>
+      <c r="B28" s="23">
+        <v>0.40722222222222221</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="25">
+        <v>0</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="22">
+        <v>45917</v>
+      </c>
+      <c r="B29" s="23">
+        <v>0.43583333333333335</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>492</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="22">
+        <v>45916</v>
+      </c>
+      <c r="B30" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>494</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>495</v>
+      </c>
+      <c r="F30" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="22">
+        <v>45915</v>
+      </c>
+      <c r="B31" s="23">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>496</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="22">
+        <v>45910</v>
+      </c>
+      <c r="B32" s="23">
+        <v>0.39812500000000001</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="F32" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="22">
+        <v>45909</v>
+      </c>
+      <c r="B33" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>500</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="22">
+        <v>45908</v>
+      </c>
+      <c r="B34" s="23">
+        <v>0.39947916666666666</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="F34" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="20"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="22">
+        <v>46056</v>
+      </c>
+      <c r="B39" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="25">
+        <v>0</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="22">
+        <v>46055</v>
+      </c>
+      <c r="B40" s="23">
+        <v>0.5721180555555555</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>506</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="22">
+        <v>46048</v>
+      </c>
+      <c r="B41" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>507</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>508</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="22">
+        <v>46030</v>
+      </c>
+      <c r="B42" s="23">
+        <v>0.40187499999999998</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="25">
+        <v>0</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>509</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="22">
+        <v>46027</v>
+      </c>
+      <c r="B43" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="25">
+        <v>0</v>
+      </c>
+      <c r="E43" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="22">
+        <v>46022</v>
+      </c>
+      <c r="B44" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>511</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>512</v>
+      </c>
+      <c r="F44" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G44" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="22">
+        <v>46021</v>
+      </c>
+      <c r="B45" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>513</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>514</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G45" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="22">
+        <v>46010</v>
+      </c>
+      <c r="B46" s="23">
+        <v>0.40059027777777778</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="25">
+        <v>0</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>515</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="22">
+        <v>46008</v>
+      </c>
+      <c r="B47" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>516</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G47" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="22">
+        <v>46007</v>
+      </c>
+      <c r="B48" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="E48" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="22">
+        <v>46006</v>
+      </c>
+      <c r="B49" s="23">
+        <v>0.43767361111111114</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="E49" s="25" t="s">
+        <v>519</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="22">
+        <v>46003</v>
+      </c>
+      <c r="B50" s="23">
+        <v>0.39982638888888888</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" s="25">
+        <v>0</v>
+      </c>
+      <c r="E50" s="25" t="s">
+        <v>520</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G50" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="22">
+        <v>46001</v>
+      </c>
+      <c r="B51" s="23">
+        <v>0.39760416666666665</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="25">
+        <v>0</v>
+      </c>
+      <c r="E51" s="25" t="s">
+        <v>521</v>
+      </c>
+      <c r="F51" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G51" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="22">
+        <v>46000</v>
+      </c>
+      <c r="B52" s="23">
+        <v>0.43204861111111109</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" s="25">
+        <v>0</v>
+      </c>
+      <c r="E52" s="25" t="s">
+        <v>522</v>
+      </c>
+      <c r="F52" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G52" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="22">
+        <v>45982</v>
+      </c>
+      <c r="B53" s="23">
+        <v>0.57885416666666667</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" s="25">
+        <v>0</v>
+      </c>
+      <c r="E53" s="25" t="s">
+        <v>523</v>
+      </c>
+      <c r="F53" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="22">
+        <v>45978</v>
+      </c>
+      <c r="B54" s="23">
+        <v>0.4123263888888889</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G54" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="22">
+        <v>45951</v>
+      </c>
+      <c r="B55" s="23">
+        <v>0.39927083333333335</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>525</v>
+      </c>
+      <c r="E55" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="F55" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G55" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="22">
+        <v>45940</v>
+      </c>
+      <c r="B56" s="23">
+        <v>0.40041666666666664</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="E56" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="F56" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="22">
+        <v>45939</v>
+      </c>
+      <c r="B57" s="23">
+        <v>0.4045138888888889</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" s="25">
+        <v>0</v>
+      </c>
+      <c r="E57" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="F57" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G57" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="22">
+        <v>45930</v>
+      </c>
+      <c r="B58" s="23">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="E58" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="F58" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G58" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="22">
+        <v>45929</v>
+      </c>
+      <c r="B59" s="23">
+        <v>0.39652777777777776</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>532</v>
+      </c>
+      <c r="E59" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="F59" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G59" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="22">
+        <v>45911</v>
+      </c>
+      <c r="B60" s="23">
+        <v>0.56538194444444445</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>534</v>
+      </c>
+      <c r="E60" s="25" t="s">
+        <v>534</v>
+      </c>
+      <c r="F60" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G60" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="22">
+        <v>45894</v>
+      </c>
+      <c r="B61" s="23">
+        <v>0.59586805555555555</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D61" s="25">
+        <v>0</v>
+      </c>
+      <c r="E61" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="F61" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G61" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="22">
+        <v>45882</v>
+      </c>
+      <c r="B62" s="23">
+        <v>0.41246527777777775</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>536</v>
+      </c>
+      <c r="E62" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="F62" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G62" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="22">
+        <v>45880</v>
+      </c>
+      <c r="B63" s="23">
+        <v>0.40027777777777779</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="25">
+        <v>0</v>
+      </c>
+      <c r="E63" s="25" t="s">
+        <v>538</v>
+      </c>
+      <c r="F63" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G63" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="22">
+        <v>45854</v>
+      </c>
+      <c r="B64" s="23">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" s="25">
+        <v>0</v>
+      </c>
+      <c r="E64" s="25" t="s">
+        <v>539</v>
+      </c>
+      <c r="F64" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G64" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="22">
+        <v>45853</v>
+      </c>
+      <c r="B65" s="23">
+        <v>0.4165625</v>
+      </c>
+      <c r="C65" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65" s="25">
+        <v>0</v>
+      </c>
+      <c r="E65" s="25" t="s">
+        <v>540</v>
+      </c>
+      <c r="F65" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G65" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="22">
+        <v>45852</v>
+      </c>
+      <c r="B66" s="23">
+        <v>0.54628472222222224</v>
+      </c>
+      <c r="C66" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D66" s="25" t="s">
+        <v>541</v>
+      </c>
+      <c r="E66" s="25" t="s">
+        <v>541</v>
+      </c>
+      <c r="F66" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G66" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="22">
+        <v>45842</v>
+      </c>
+      <c r="B67" s="23">
+        <v>0.40989583333333335</v>
+      </c>
+      <c r="C67" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" s="25">
+        <v>0</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>542</v>
+      </c>
+      <c r="F67" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G67" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="22">
+        <v>45831</v>
+      </c>
+      <c r="B68" s="23">
+        <v>0.46319444444444446</v>
+      </c>
+      <c r="C68" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D68" s="25">
+        <v>0</v>
+      </c>
+      <c r="E68" s="25" t="s">
+        <v>543</v>
+      </c>
+      <c r="F68" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G68" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB6949E8-52B8-4B0E-8F3A-D614A94473A0}">
+  <dimension ref="A1:G58"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="175.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.47045138888888888</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>46098</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.54575231481481479</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0.43076388888888889</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0.45983796296296298</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>46087</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.42854166666666665</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B10" s="8">
+        <v>0.4001851851851852</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>46057</v>
+      </c>
+      <c r="B11" s="8">
+        <v>0.40945601851851854</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>46056</v>
+      </c>
+      <c r="B12" s="8">
+        <v>0.55307870370370371</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>46044</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0.56380787037037039</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>46036</v>
+      </c>
+      <c r="B14" s="8">
+        <v>0.43493055555555554</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>46034</v>
+      </c>
+      <c r="B15" s="8">
+        <v>0.40032407407407405</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>46028</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0.42625000000000002</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>46027</v>
+      </c>
+      <c r="B17" s="8">
+        <v>0.5783449074074074</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>46020</v>
+      </c>
+      <c r="B18" s="8">
+        <v>0.59047453703703701</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>46002</v>
+      </c>
+      <c r="B19" s="8">
+        <v>0.45744212962962966</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>45992</v>
+      </c>
+      <c r="B20" s="8">
+        <v>0.4001736111111111</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>45989</v>
+      </c>
+      <c r="B21" s="8">
+        <v>0.39837962962962964</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>45988</v>
+      </c>
+      <c r="B22" s="8">
+        <v>0.39622685185185186</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>45987</v>
+      </c>
+      <c r="B23" s="8">
+        <v>0.39629629629629631</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>45986</v>
+      </c>
+      <c r="B24" s="8">
+        <v>0.4019212962962963</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>45985</v>
+      </c>
+      <c r="B25" s="8">
+        <v>0.40131944444444445</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>45980</v>
+      </c>
+      <c r="B26" s="8">
+        <v>0.40383101851851849</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>45979</v>
+      </c>
+      <c r="B27" s="8">
+        <v>0.40569444444444447</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>45975</v>
+      </c>
+      <c r="B28" s="8">
+        <v>0.3967013888888889</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>45974</v>
+      </c>
+      <c r="B29" s="8">
+        <v>0.40681712962962963</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>45973</v>
+      </c>
+      <c r="B30" s="8">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>45972</v>
+      </c>
+      <c r="B31" s="8">
+        <v>0.39239583333333333</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>45971</v>
+      </c>
+      <c r="B32" s="8">
+        <v>0.3964699074074074</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>45964</v>
+      </c>
+      <c r="B33" s="8">
+        <v>0.4753472222222222</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>45951</v>
+      </c>
+      <c r="B34" s="8">
+        <v>0.39641203703703703</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="10">
+        <v>0</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A35" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>46065</v>
+      </c>
+      <c r="B39" s="4">
+        <v>0.62287037037037041</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>46058</v>
+      </c>
+      <c r="B40" s="8">
+        <v>0.39740740740740743</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="10">
+        <v>0</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>46051</v>
+      </c>
+      <c r="B41" s="8">
+        <v>0.61563657407407413</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="10">
+        <v>0</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>46050</v>
+      </c>
+      <c r="B42" s="8">
+        <v>0.57158564814814816</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="10">
+        <v>0</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>46045</v>
+      </c>
+      <c r="B43" s="8">
+        <v>0.3923726851851852</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="10">
+        <v>0</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>46043</v>
+      </c>
+      <c r="B44" s="8">
+        <v>0.3923726851851852</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>46042</v>
+      </c>
+      <c r="B45" s="8">
+        <v>0.39238425925925924</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>46041</v>
+      </c>
+      <c r="B46" s="8">
+        <v>0.39239583333333333</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>46038</v>
+      </c>
+      <c r="B47" s="8">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>46037</v>
+      </c>
+      <c r="B48" s="8">
+        <v>0.39239583333333333</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>46021</v>
+      </c>
+      <c r="B49" s="8">
+        <v>0.41172453703703704</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" s="10">
+        <v>0</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>46003</v>
+      </c>
+      <c r="B50" s="8">
+        <v>0.40072916666666669</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>45982</v>
+      </c>
+      <c r="B51" s="8">
+        <v>0.39853009259259259</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="10">
+        <v>0</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
+        <v>45981</v>
+      </c>
+      <c r="B52" s="8">
+        <v>0.57673611111111112</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
+        <v>45978</v>
+      </c>
+      <c r="B53" s="8">
+        <v>0.41291666666666665</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" s="10">
+        <v>0</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="7">
+        <v>45922</v>
+      </c>
+      <c r="B54" s="8">
+        <v>0.416875</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
+        <v>45854</v>
+      </c>
+      <c r="B55" s="8">
+        <v>0.45197916666666665</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" s="10">
+        <v>0</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="7">
+        <v>45853</v>
+      </c>
+      <c r="B56" s="8">
+        <v>0.39861111111111114</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="7">
+        <v>45754</v>
+      </c>
+      <c r="B57" s="8">
+        <v>0.40697916666666667</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="7">
+        <v>45398</v>
+      </c>
+      <c r="B58" s="8">
+        <v>0.41171296296296295</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="10">
+        <v>0</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/Fundamentals/2025百大牛股/2025年百大牛股.xlsx
+++ b/docs/Fundamentals/2025百大牛股/2025年百大牛股.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\warrenpyquant\examples\warrenluccie.github.io\docs\Fundamentals\2025百大牛股\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\【0#】DeepReview深度复盘\warrenluccie.github.io\docs\Fundamentals\2025百大牛股\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E012791-7006-4D27-BC26-16983F930F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841FBF49-D743-4DD2-ACB5-0A2DF75FF129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="954" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="954" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="上纬新材 688585" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name=" ST亚振 603389" sheetId="5" r:id="rId5"/>
     <sheet name="ST宇顺 002289" sheetId="6" r:id="rId6"/>
     <sheet name="国晟科技 603778" sheetId="7" r:id="rId7"/>
+    <sheet name="宏和科技 603256" sheetId="8" r:id="rId8"/>
+    <sheet name="舒泰神 300204" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="788">
   <si>
     <t>发生日期</t>
   </si>
@@ -2241,6 +2243,485 @@
         <charset val="134"/>
       </rPr>
       <t>储能</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.54亿</t>
+  </si>
+  <si>
+    <t>玻璃玻纤</t>
+  </si>
+  <si>
+    <t>国内少数具备Low CTE电子布等量产能力的生产企业之一</t>
+  </si>
+  <si>
+    <t>6874.94万</t>
+  </si>
+  <si>
+    <t>6.86亿</t>
+  </si>
+  <si>
+    <t>1、据2026年3月28日公告，公司拟与黄石经开区签订《项目投资协议书》，通过子公司黄石宏和投资约80亿元建设“高性能电子材料产业园”，新增高性能电子纱及电子布产能。 2、据2025年1月29日业绩预增公告，公司预计2025年归母净利1.93-2.25亿元，同比增长745%-889%，主因AI服务器、高频高速需求带动电子级玻璃纤维布量价齐升。 3、据2025年4月29日年报，公司主营中高端电子级玻璃纤维布、电子级玻璃纤维超细纱，已实现电子纱-电子布一体化，产品用于智能手机、服务器、5G基站、IC封装等高端PCB领域。</t>
+  </si>
+  <si>
+    <t>8179.23万</t>
+  </si>
+  <si>
+    <t>5.28亿</t>
+  </si>
+  <si>
+    <t>玻璃玻纤+AI算力+PCB概念</t>
+  </si>
+  <si>
+    <t>行业称在25年涨价50%的基础上，电子布月度价格继续上调10-15%|1、据2026年1月29日业绩预增公告，公司预计2025年归母净利1.93-2.26亿元，同比增745%-889%，主因AI需求带动电子级玻璃纤维布量价齐升。 2、据2026年2月4日互动易，公司Q布产能充足，石英布已通过PCB端测试并送终端客户认证，性能超越部分日企。 3、据2025年半年度报告，公司实现电子纱、电子布一体化生产，产品用于智能手机、服务器、5G基站、IC封装等高端领域。</t>
+  </si>
+  <si>
+    <t>9098.67万</t>
+  </si>
+  <si>
+    <t>2.90亿</t>
+  </si>
+  <si>
+    <t>玻璃玻纤+AI算力+业绩预增</t>
+  </si>
+  <si>
+    <t>电子布需求持续增长；台耀调整E-glass生产计划|1、据2026年1月29日业绩预增公告，公司预计2025年归母净利1.93-2.25亿元，同比增745%-889%，主因AI需求带动电子级玻璃纤维布量价齐升。 2、据2026年2月10日公告，子公司黄石宏和获“低热膨胀系数玻璃纤维拉丝漏板及窑炉”发明专利，强化高端电子布技术壁垒。 3、据2025年半年度报告，公司主营中高端电子级玻璃纤维布及纱，已实现电子纱、电子布一体化生产，产品应用于智能手机、服务器、5G基站、IC芯片封装等高端领域，与华为等终端品牌长期合作。</t>
+  </si>
+  <si>
+    <t>5.77亿</t>
+  </si>
+  <si>
+    <t>6.75亿</t>
+  </si>
+  <si>
+    <t>日本半导体材料厂调涨CCL、黏合胶片等PCB材料售价30%以上|国内少数具备Low CTE电子布等量产能力的生产企业之一</t>
+  </si>
+  <si>
+    <t>1.59亿</t>
+  </si>
+  <si>
+    <t>8.52亿</t>
+  </si>
+  <si>
+    <t>玻璃玻纤+AI服务器+PCB概念</t>
+  </si>
+  <si>
+    <t>日本半导体材料厂调涨CCL、黏合胶片等PCB材料售价30%以上|1、据2026年1月14日募集说明书注册稿，公司定增募资建设高性能玻纤纱产线及研发中心，投产后将显著扩大低介电、低热膨胀系数电子布产能，相关产品已通过部分客户认证，直接受益AI服务器、高频通信需求增长。 2、据2025年4月12日可行性分析报告，公司主营中高端电子级玻璃纤维布及纱，已实现电子纱、电子布一体化生产，产品应用于服务器、5G基站、IC芯片封装等高端领域，已全面进入全球领先PCB厂商供应链。 3、据2025年三季报，公司前三季度营收8.52亿元，同比增长37.76%；归母净利润1.39亿元，同比增长1696.45%，业绩大幅提升。</t>
+  </si>
+  <si>
+    <t>7329.36万</t>
+  </si>
+  <si>
+    <t>5.69亿</t>
+  </si>
+  <si>
+    <t>玻璃玻纤+PCB概念+高端电子布</t>
+  </si>
+  <si>
+    <t>日本半导体材料厂Resonac调涨印刷电路板（PCB）材料售价30%以上|1、据2026年1月14日募集说明书注册稿，公司定增募资建设高性能玻纤纱产线及研发中心，投产后将显著扩大低介电、低热膨胀系数电子布产能，相关产品已通过部分客户认证。 2、据2025年8月28日2025年半年度报告，公司主营中高端电子级玻璃纤维布及纱，已实现电子纱、电子布一体化，产品用于PCB、芯片封装、高速服务器等高端领域，客户包括生益科技、松下、南亚新材等全球前十覆铜板厂商。 3、据2025年8月28日2025年半年度报告，公司2024年高性能电子级低介电常数玻璃纤维布和低热膨胀系数玻璃纤维布已获下游客户认证通过，2025年上半年开始批量供应并依据市场需求扩充产能。</t>
+  </si>
+  <si>
+    <t>3.56亿</t>
+  </si>
+  <si>
+    <t>1、据2026年1月14日募集说明书注册稿，公司定增募资建设高性能玻纤纱产线及研发中心，项目投产后将显著扩大低介电、低热膨胀系数电子布产能，相关产品已通过部分客户认证。 2、据2025年半年度报告，公司实现了电子纱、电子布一体化生产和经营。2024年公司高性能电子级低介电常数玻璃纤维布和低热膨胀系数玻璃纤维布已获得下游客户的认证通过。2025年开始批量供应给下游客户。并依据市场需求状况扩充产能，满足客户对高端电子布的需求。 3、据2025年半年度报告，公司主营中高端电子级玻璃纤维布及纱，已实现电子纱、电子布一体化，产品用于PCB、芯片封装、高速服务器等高端领域，客户包括生益科技、松下、南亚新材等全球前十覆铜板厂商。 4、据公司2025年半年报，公司实控人GraceTsuHanWong，王文洋为台湾籍。</t>
+  </si>
+  <si>
+    <t>65.89万</t>
+  </si>
+  <si>
+    <t>PCB概念+高性能电子布+华为概念</t>
+  </si>
+  <si>
+    <t>PCB关键原材料玻纤布供应紧张 特种玻纤布迎量价齐升趋势</t>
+  </si>
+  <si>
+    <t>3477.66万</t>
+  </si>
+  <si>
+    <t>玻璃玻纤+PCB概念+海峡西岸</t>
+  </si>
+  <si>
+    <t>1、据2025年半年度报告，公司实现了电子纱、电子布一体化生产和经营。2024年公司高性能电子级低介电常数玻璃纤维布和低热膨胀系数玻璃纤维布已获得下游客户的认证通过。2025年开始批量供应给下游客户。并依据市场需求状况扩充产能，满足客户对高端电子布的需求。 2、据2025年半年度报告，公司主营中高端电子级玻璃纤维布及纱，已实现电子纱、电子布一体化，产品用于PCB、芯片封装、高速服务器等高端领域，客户包括生益科技、松下、南亚新材等全球前十覆铜板厂商。 3、据公司2025年半年报，公司实控人GraceTsuHanWong，王文洋为台湾籍。</t>
+  </si>
+  <si>
+    <t>7386.53万</t>
+  </si>
+  <si>
+    <t>6.12亿</t>
+  </si>
+  <si>
+    <t>玻璃玻纤+PCB概念+三季报增长</t>
+  </si>
+  <si>
+    <t>1、宏和科技相关负责人透露，公司高性能产品“低介电一代”价格是普通产品的6倍，低介电二代和低热膨胀系数因市场比较稀缺，价格仍在上涨。高阶覆铜板方面，有A股厂商人士称，目前AI、机器人等应用场景的基础材料轻薄化，尤其算力板块对高性能产品的需求量增加。因产品的非通用性，生产制造设备及工艺都要匹配市场慢慢进行调整，产能目前有限。 1、据2025年半年度报告，公司主营中高端电子级玻璃纤维布及纱，已实现电子纱、电子布一体化，产品用于PCB、芯片封装、高速服务器等高端领域，客户包括生益科技、松下、南亚新材等全球前十覆铜板厂商。 2、据2025年10月30日三季报，公司前三季度营收8.52亿元，同比增长37.76%；归母净利润1.39亿元，同比增长1696.45%。 3、据公司2025年半年报，公司实控人GraceTsuHanWong，王文洋为台湾籍。</t>
+  </si>
+  <si>
+    <t>7063.90万</t>
+  </si>
+  <si>
+    <t>5.23亿</t>
+  </si>
+  <si>
+    <t>PCB概念+玻璃纤维布+三季报增长</t>
+  </si>
+  <si>
+    <t>1、据2025年半年度报告，公司主营中高端电子级玻璃纤维布及纱，已实现电子纱、电子布一体化，产品用于PCB、芯片封装、高速服务器等高端领域，客户包括生益科技、松下、南亚新材等全球前十覆铜板厂商。 2、据2025年10月30日三季报，公司前三季度营收8.52亿元，同比增长37.76%；归母净利润1.39亿元，同比增长1696.45%。 3、据公司2025年半年报，公司实控人GraceTsuHanWong，王文洋为台湾籍。</t>
+  </si>
+  <si>
+    <t>玻璃玻纤+PCB概念+半年报增长</t>
+  </si>
+  <si>
+    <t>英伟达展示下一代GPU架构Rubin，预计出货2000万块|国内少数具备Low CTE电子布等量产能力的生产企业之一</t>
+  </si>
+  <si>
+    <t>8958.53万</t>
+  </si>
+  <si>
+    <t>4.25亿</t>
+  </si>
+  <si>
+    <t>龙头业绩大增；英伟达下一代GPU架构Rubin生产或提速|国内少数具备Low CTE电子布等量产能力的生产企业之一</t>
+  </si>
+  <si>
+    <t>4.80亿</t>
+  </si>
+  <si>
+    <t>玻璃玻纤+半年报大增+扩产</t>
+  </si>
+  <si>
+    <t>全球领先的中高端电子级玻璃纤维布专业厂商 ；公司主要从事电子级玻璃纤维产品的生产与销售，产品具有绝缘、增强等特性，是覆铜板核心原材料，广泛应用于 AI 服务器、5G 基站、汽车电子等领域的 PCB 制造，已为深南电路等知名企业供货</t>
+  </si>
+  <si>
+    <t>6580.29万</t>
+  </si>
+  <si>
+    <t>4.12亿</t>
+  </si>
+  <si>
+    <t>玻璃纤维布+半年报大增</t>
+  </si>
+  <si>
+    <t>英伟达发布Rubin CPX；甲骨文积压订单超4500亿美元，股价大涨36%|全球领先的中高端电子级玻璃纤维布专业厂商 ；公司主要从事电子级玻璃纤维产品的生产与销售，产品具有绝缘、增强等特性，是覆铜板核心原材料，广泛应用于 AI 服务器、5G 基站、汽车电子等领域的 PCB 制造，已为深南电路等知名企业供货</t>
+  </si>
+  <si>
+    <t>8156.06万</t>
+  </si>
+  <si>
+    <t>2.58亿</t>
+  </si>
+  <si>
+    <t>苹果概念+玻璃玻纤+半年报大增</t>
+  </si>
+  <si>
+    <t>Low CTE等PCB上游材料供不应求|全球领先的中高端电子级玻璃纤维布专业厂商 ；公司主要从事电子级玻璃纤维产品的生产与销售，产品具有绝缘、增强等特性，是覆铜板核心原材料，广泛应用于 AI 服务器、5G 基站、汽车电子等领域的 PCB 制造，已为深南电路等知名企业供货</t>
+  </si>
+  <si>
+    <t>玻璃纤维布+PCB概念+一季报增长</t>
+  </si>
+  <si>
+    <t>1.30亿</t>
+  </si>
+  <si>
+    <t>玻璃玻纤+PCB概念+一季报增长</t>
+  </si>
+  <si>
+    <t>1.01亿</t>
+  </si>
+  <si>
+    <t>2.06亿</t>
+  </si>
+  <si>
+    <t>6184.29万</t>
+  </si>
+  <si>
+    <t>2.57亿</t>
+  </si>
+  <si>
+    <t>5.59亿</t>
+  </si>
+  <si>
+    <t>Open AI称未来5个月要将算力扩大一倍|全球领先的中高端电子级玻璃纤维布专业厂商 ；公司主要从事电子级玻璃纤维产品的生产与销售，产品具有绝缘、增强等特性，是覆铜板核心原材料，广泛应用于 AI 服务器、5G 基站、汽车电子等领域的 PCB 制造，已为深南电路等知名企业供货</t>
+  </si>
+  <si>
+    <t>5581.68万</t>
+  </si>
+  <si>
+    <t>9532.60万</t>
+  </si>
+  <si>
+    <t>微软、Meta等业绩和资本开支超预期|全球领先的中高端电子级玻璃纤维布专业厂商 ；公司主要从事电子级玻璃纤维产品的生产与销售，产品具有绝缘、增强等特性，是覆铜板核心原材料，广泛应用于 AI 服务器、5G 基站、汽车电子等领域的 PCB 制造，已为深南电路等知名企业供货</t>
+  </si>
+  <si>
+    <t>3.54亿</t>
+  </si>
+  <si>
+    <t>PCB概念+高性能玻纤布+一季报增长</t>
+  </si>
+  <si>
+    <t>514.82万</t>
+  </si>
+  <si>
+    <t>2.59亿</t>
+  </si>
+  <si>
+    <t>2.61亿</t>
+  </si>
+  <si>
+    <t>AI服务器应用带动low DK电子布产品持续放量|公司为全球领先的中高端电子级玻璃纤维布厂商，高端电子布（超薄布和极薄布）市场占有率全球第一</t>
+  </si>
+  <si>
+    <t>1.47万</t>
+  </si>
+  <si>
+    <t>PCB概念</t>
+  </si>
+  <si>
+    <t>超5000亿元龙头异动！最新业绩大幅预增股来了</t>
+  </si>
+  <si>
+    <t>8882.37万</t>
+  </si>
+  <si>
+    <t>2.86亿</t>
+  </si>
+  <si>
+    <t>玻璃玻纤+消费电子概念</t>
+  </si>
+  <si>
+    <t>3451.01万</t>
+  </si>
+  <si>
+    <t>2.78亿</t>
+  </si>
+  <si>
+    <t>AI等应用带动low DK电子布产品持续放量|公司为全球领先的中高端电子级玻璃纤维布厂商，高端电子布（超薄布和极薄布）市场占有率全球第一</t>
+  </si>
+  <si>
+    <t>1.49亿</t>
+  </si>
+  <si>
+    <t>24.75万</t>
+  </si>
+  <si>
+    <t>2668.11万</t>
+  </si>
+  <si>
+    <t>2538.30万</t>
+  </si>
+  <si>
+    <t>2826.89万</t>
+  </si>
+  <si>
+    <t>1370.68万</t>
+  </si>
+  <si>
+    <t>1.14亿</t>
+  </si>
+  <si>
+    <t>393.13万</t>
+  </si>
+  <si>
+    <t>398.82万</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玻璃玻纤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>+PCB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>概念</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>+80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿产业园</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>创新药</t>
+  </si>
+  <si>
+    <t>公司是创新药物研发公司</t>
+  </si>
+  <si>
+    <t>1.04亿</t>
+  </si>
+  <si>
+    <t>10.79亿</t>
+  </si>
+  <si>
+    <t>创新药+STSP-0601+STSP-0902</t>
+  </si>
+  <si>
+    <t>2026年中国创新药出海BD总包已达571亿美元；AACR年会将召开|公司发布STSA-1002注射液在急性呼吸窘迫综合征（ARDS）适应症下获得了Ib/II期临床试验研究的初步结果</t>
+  </si>
+  <si>
+    <t>1.27亿</t>
+  </si>
+  <si>
+    <t>14.50亿</t>
+  </si>
+  <si>
+    <t>创新药+定增受理+STSP-0601</t>
+  </si>
+  <si>
+    <t>2025国家医保谈判启动，引入“商保创新药目录”机制| 1、据2025年10月27日公告，公司向特定对象发行股票申请获深交所受理，拟募资12.53亿元用于BDB-001、STSA-1002、STSP-0902等创新药III期临床及上市申报，加速产品商业化。 2、据2025年10月28日互动易，注射用STSP-0601波米泰酶α附条件上市申请已获国家药监局受理并进入优先审评，130日审评倒计时已启动。 3、据2025年8月26日半年报，公司主营创新生物药苏肽生、舒泰清，并围绕神经系统、呼吸与重症、感染及自身免疫等领域构建差异化研发管线，拥有77件授权专利及多项突破性疗法认定。</t>
+  </si>
+  <si>
+    <t>1.71亿</t>
+  </si>
+  <si>
+    <t>国产创新药出海大单频出|公司发布STSA-1002注射液在急性呼吸窘迫综合征（ARDS）适应症下获得了Ib/II期临床试验研究的初步结果</t>
+  </si>
+  <si>
+    <t>A股创新药企业多点开花，机构称板块景气度可持续</t>
+  </si>
+  <si>
+    <t>21.48万</t>
+  </si>
+  <si>
+    <t>国家药监局征求意见：纳入创新药临床试验审评审批30日通道的申请</t>
+  </si>
+  <si>
+    <t>前期暴炒股</t>
+  </si>
+  <si>
+    <t>2025-05-21到2025-06-09,该股炒作概念为创新药。</t>
+  </si>
+  <si>
+    <t>1369.65万</t>
+  </si>
+  <si>
+    <t>创新药密集获批；龙头出海现成效|子公司参股公司新冠治疗药物Gohibic注射液获FDA紧急使用授权</t>
+  </si>
+  <si>
+    <t>9816.02万</t>
+  </si>
+  <si>
+    <t>创新药概念再度走强，联化科技4连板，舒泰神等大涨</t>
+  </si>
+  <si>
+    <t>尾盘！批量涨停！</t>
+  </si>
+  <si>
+    <t>4622.75万</t>
+  </si>
+  <si>
+    <t>3.50亿</t>
+  </si>
+  <si>
+    <t>创新药+血友病治疗药物+基因治疗</t>
+  </si>
+  <si>
+    <t>三生制药与辉瑞签署合作协议，刷新中国创新药对外授权金额记录|子公司参股公司新冠治疗药物Gohibic注射液获FDA紧急使用授权</t>
+  </si>
+  <si>
+    <t>最新筹码集中股名单发布！</t>
+  </si>
+  <si>
+    <t>5271.16万</t>
+  </si>
+  <si>
+    <t>14.26亿</t>
+  </si>
+  <si>
+    <t>创新药+免疫治疗</t>
+  </si>
+  <si>
+    <t>生物制品</t>
+  </si>
+  <si>
+    <t>公司所属行业为：生物制品</t>
+  </si>
+  <si>
+    <t>4611.79万</t>
+  </si>
+  <si>
+    <t>10.30亿</t>
+  </si>
+  <si>
+    <t>创新药+白血病药物</t>
+  </si>
+  <si>
+    <t>创新药集采政策转向提质|子公司参股公司新冠治疗药物Gohibic注射液获FDA紧急使用授权</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>创新药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>血友病治疗药物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>免疫治疗</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -10320,7 +10801,7 @@
     <col min="7" max="7" width="175.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>5</v>
       </c>
@@ -11062,7 +11543,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>62</v>
       </c>
@@ -11578,4 +12059,1952 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D563D3EB-284F-4CF0-8CDA-5DD14D8640DF}">
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.875" customWidth="1"/>
+    <col min="7" max="7" width="79.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.39614583333333331</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>46111</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.40797453703703701</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>661</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>750</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>46077</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0.41143518518518518</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>46065</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0.40134259259259258</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>46064</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.39752314814814815</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>46063</v>
+      </c>
+      <c r="B10" s="8">
+        <v>0.43131944444444442</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>46050</v>
+      </c>
+      <c r="B11" s="8">
+        <v>0.4753472222222222</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>46044</v>
+      </c>
+      <c r="B12" s="8">
+        <v>0.56049768518518517</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>679</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>46043</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0.6108217592592593</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>46037</v>
+      </c>
+      <c r="B14" s="8">
+        <v>0.39839120370370368</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>684</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>46014</v>
+      </c>
+      <c r="B15" s="8">
+        <v>0.43527777777777776</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>45999</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0.44636574074074076</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>690</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>45986</v>
+      </c>
+      <c r="B17" s="8">
+        <v>0.44114583333333335</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>695</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>45959</v>
+      </c>
+      <c r="B18" s="8">
+        <v>0.39627314814814812</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>45958</v>
+      </c>
+      <c r="B19" s="8">
+        <v>0.41106481481481483</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>45918</v>
+      </c>
+      <c r="B20" s="8">
+        <v>0.44776620370370368</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>45911</v>
+      </c>
+      <c r="B21" s="8">
+        <v>0.40854166666666669</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>45897</v>
+      </c>
+      <c r="B22" s="8">
+        <v>0.5715972222222222</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>45891</v>
+      </c>
+      <c r="B23" s="8">
+        <v>0.40033564814814815</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>45887</v>
+      </c>
+      <c r="B24" s="8">
+        <v>0.3923726851851852</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="10">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>715</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>45884</v>
+      </c>
+      <c r="B25" s="8">
+        <v>0.39905092592592595</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>45883</v>
+      </c>
+      <c r="B26" s="8">
+        <v>0.39634259259259258</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>45882</v>
+      </c>
+      <c r="B27" s="8">
+        <v>0.45953703703703702</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>721</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>45875</v>
+      </c>
+      <c r="B28" s="8">
+        <v>0.61829861111111106</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>724</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>45870</v>
+      </c>
+      <c r="B29" s="8">
+        <v>0.40546296296296297</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>45869</v>
+      </c>
+      <c r="B30" s="8">
+        <v>0.3963888888888889</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>729</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>45866</v>
+      </c>
+      <c r="B31" s="8">
+        <v>0.61763888888888885</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>45847</v>
+      </c>
+      <c r="B32" s="8">
+        <v>0.55585648148148148</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="10">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>45846</v>
+      </c>
+      <c r="B33" s="8">
+        <v>0.41001157407407407</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>45845</v>
+      </c>
+      <c r="B34" s="8">
+        <v>0.39702546296296298</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A35" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B39" s="4">
+        <v>0.41609953703703706</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>45874</v>
+      </c>
+      <c r="B40" s="8">
+        <v>0.6116435185185185</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>45848</v>
+      </c>
+      <c r="B41" s="8">
+        <v>0.61283564814814817</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>45754</v>
+      </c>
+      <c r="B42" s="8">
+        <v>0.40747685185185184</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>45478</v>
+      </c>
+      <c r="B43" s="8">
+        <v>0.39238425925925924</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>747</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>45398</v>
+      </c>
+      <c r="B44" s="8">
+        <v>0.41131944444444446</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A671B683-4AE4-4D6B-9FFC-1E708FE2107E}">
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.75" customWidth="1"/>
+    <col min="7" max="7" width="45.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.5649305555555556</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>754</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>45971</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>45961</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0.54746527777777776</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>45947</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>45945</v>
+      </c>
+      <c r="B10" s="8">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>45911</v>
+      </c>
+      <c r="B11" s="8">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>45894</v>
+      </c>
+      <c r="B12" s="8">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>45888</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0.44694444444444442</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>761</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>45870</v>
+      </c>
+      <c r="B14" s="8">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>45869</v>
+      </c>
+      <c r="B15" s="8">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>45841</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>45839</v>
+      </c>
+      <c r="B17" s="8">
+        <v>0.60947916666666668</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>764</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>45825</v>
+      </c>
+      <c r="B18" s="8">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>45821</v>
+      </c>
+      <c r="B19" s="8">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>45820</v>
+      </c>
+      <c r="B20" s="8">
+        <v>0</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>45817</v>
+      </c>
+      <c r="B21" s="8">
+        <v>0.62121527777777774</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>787</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>45813</v>
+      </c>
+      <c r="B22" s="8">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>45811</v>
+      </c>
+      <c r="B23" s="8">
+        <v>0.58211805555555551</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>770</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>45807</v>
+      </c>
+      <c r="B24" s="8">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="10">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>45806</v>
+      </c>
+      <c r="B25" s="8">
+        <v>0.40510416666666665</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>45804</v>
+      </c>
+      <c r="B26" s="8">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>45800</v>
+      </c>
+      <c r="B27" s="8">
+        <v>0</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>45799</v>
+      </c>
+      <c r="B28" s="8">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="10">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>45798</v>
+      </c>
+      <c r="B29" s="8">
+        <v>0.40416666666666667</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>45797</v>
+      </c>
+      <c r="B30" s="8">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="10">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>45786</v>
+      </c>
+      <c r="B31" s="8">
+        <v>0</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="10">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>45771</v>
+      </c>
+      <c r="B32" s="8">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="10">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>45768</v>
+      </c>
+      <c r="B33" s="8">
+        <v>0.42913194444444447</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>785</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>45765</v>
+      </c>
+      <c r="B34" s="8">
+        <v>0</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="10">
+        <v>0</v>
+      </c>
+      <c r="E34" s="10">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A35" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>45953</v>
+      </c>
+      <c r="B39" s="4">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>45905</v>
+      </c>
+      <c r="B40" s="8">
+        <v>0</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="10">
+        <v>0</v>
+      </c>
+      <c r="E40" s="10">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>45902</v>
+      </c>
+      <c r="B41" s="8">
+        <v>0</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" s="10">
+        <v>0</v>
+      </c>
+      <c r="E41" s="10">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>45889</v>
+      </c>
+      <c r="B42" s="8">
+        <v>0</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="10">
+        <v>0</v>
+      </c>
+      <c r="E42" s="10">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>45832</v>
+      </c>
+      <c r="B43" s="8">
+        <v>0</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" s="10">
+        <v>0</v>
+      </c>
+      <c r="E43" s="10">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>45789</v>
+      </c>
+      <c r="B44" s="8">
+        <v>0</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="10">
+        <v>0</v>
+      </c>
+      <c r="E44" s="10">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>45754</v>
+      </c>
+      <c r="B45" s="8">
+        <v>0</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" s="10">
+        <v>0</v>
+      </c>
+      <c r="E45" s="10">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>45574</v>
+      </c>
+      <c r="B46" s="8">
+        <v>0</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" s="10">
+        <v>0</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>